--- a/EAL_제품_메이커_정리_6척.xlsx
+++ b/EAL_제품_메이커_정리_6척.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EAL 제품·메이커" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="선박별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="한눈에 보기" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EAL 제품·메이커" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="선박별 상세" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Klüber·SKF 참조" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -84,8 +86,44 @@
       <color rgb="001F3864"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001F7A3D"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00BF8F00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001F7A3D"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -125,6 +163,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -187,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -198,6 +241,53 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -207,28 +297,13 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -237,19 +312,29 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -616,6 +701,1057 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EAL 적용 한눈에 보기 — 부위별 요약 및 Klüber · SKF 승인 대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>※ 선박 6척 · 적용 60건을 「적용 부위」 기준으로 압축한 표입니다. 건별 원문은 '선박별 상세' 시트를 보십시오.
+※ Klüber 승인 = 해당 장비 메이커가 Klüber EAL 제품을 승인했는지 · SKF 등재 = 현재 사용 제품이 SKF Marine EAL 리스트에 있는지</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>적용 부위</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>현재 사용 제품</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>오일 메이커</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>적용 선박</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>장비 메이커</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Klüber 대응 제품</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Klüber 승인 (장비 메이커 기준)</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>SKF Marine EAL 리스트 등재</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Stern Tube
+(선미관)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>BIONEPTAN 150</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>SK AUDACE</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>WÄRTSILÄ</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio RM 2-150</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>승인 — Wärtsilä Japan · Sweden(Cedervall) · UK
+(BIO FKM seal rings)</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>등재 — Bioneptan 150 / 150 cSt /
+Sterntube Oil / FKM Pod · FKM Bio</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>승인 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>ATLANTA MARINE D 3005
+Melina S 30 · Veritas 800 Marine 30</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>TotalEnergies / Shell /
+Chevron</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>나머지 5척</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>KEMEL · WÄRTSILÄ</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Klüberbio RM 2-100 / RM 2-150</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>승인 — KEMEL(선박별 개별승인 필요) ·
+Wärtsilä · SKF Marine(Simplex)</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>해당 없음 (광유는 EAL 아님)</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>검토 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Bow Thruster
+— 기어유</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>BIONEPTAN HT 100</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>PRISM AGILITY
+SK AUDACE</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>KHI</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio EG 2-100</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>승인 — Kawasaki Heavy Industries
+(2018-02 및 2018-08 자료 모두 확인)</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>등재 — Bioneptan HT 100 / 100 cSt /
+Multipurpose Oil</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>승인 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>MOBIL SHC AWARE GEAR 100</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>PRISM AGILITY
+(초기 충전유)</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>KHI</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio EG 2-100</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>승인 — Kawasaki Heavy Industries</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>등재 — Mobil SHC Aware Gear 100 /
+100 cSt / Gear Oil</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>승인 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Bow Thruster
+— 그리스</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>BIOMULTIS EP 2</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>PRISM AGILITY
+SK AUDACE</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>KHI</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio AG 39-602 계열</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>자료 내 KHI 그리스 승인 없음</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>대상 아님 (SKF 리스트는 오일 전용)</t>
+        </is>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Propeller Cap /
+Bonnet</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>BIOMULTIS EP 2</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>AL SAKHAMAH
+BU FINTAS</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>SILLA METAL CO.</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio BM 32-142 /
+AG 39-602 / LG 39-701 N</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>자료 내 SILLA METAL 없음
+(승인: MAN D&amp;T · Mecklenburger Metallguss ·
+Sistemar · Stone Marine)</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>대상 아님 (그리스)</t>
+        </is>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="17" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Shell Naturelle S5 Grease
+V120P 2</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>PUTERI SABAH</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>HHI (EMD)</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio BM 32-142 /
+AG 39-602 / LG 39-701 N</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>자료 내 HHI (EMD) 없음</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>대상 아님 (그리스)</t>
+        </is>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>CLARITY SYN EA GREASE</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>MARVEL DOVE</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>HHI-EMD</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio BM 32-142 /
+AG 39-602 / LG 39-701 N</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>자료 내 HHI-EMD 없음</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>대상 아님 (그리스)</t>
+        </is>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Rudder Carrier</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>CLARITY SYN EA GREASE 0</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>MARVEL DOVE</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>3K INDUSTRY</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio LG 39-701 N</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>승인 — 3K / Korea
+(rudder shaft and pump)</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>대상 아님 (그리스)</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>승인 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="17" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>HOUTON TECTYL G OS 5550 ECO</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Houghton (Tectyl)</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>PRISM AGILITY</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>3K INDUSTRY</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio LG 39-701 N</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>승인 — 3K / Korea
+(rudder shaft and pump)</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>대상 아님 (그리스)</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>승인 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="17" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Margrease EP 0</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>PUTERI SABAH</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>3K Industry</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio LG 39-701 N</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>승인 — 3K / Korea
+(rudder shaft and pump)</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>대상 아님 (그리스)</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>승인 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="17" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>MOBIL SHC AWARE GREASE EP 2</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>SK AUDACE</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>FLUTEK</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio LG 39-701 N /
+AG 39-602</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>자료 내 FLUTEK 없음</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>대상 아님 (그리스)</t>
+        </is>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>BIOMULTIS EP 2</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>BU FINTAS</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>MACGREGOR</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio LG 39-701 N /
+AG 39-602</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>자료 내 MACGREGOR 없음</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>대상 아님 (그리스)</t>
+        </is>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Rudder Carrier
+(Rudder Trunk)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>BIOADHESIVE PLUS</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>AL SAKHAMAH</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>FLUTEK</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio LG 39-701 N /
+AG 39-602</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>자료 내 FLUTEK 없음</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>대상 아님 (그리스)</t>
+        </is>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Wire Ropes /
+Towing Wire</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>BIOADHESIVE PLUS</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>AL SAKHAMAH
+BU FINTAS
+SK AUDACE</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>ORIENTAL · TANKTECH 등</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Klüber 자료 범위 밖</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>— (Klüber 자료는 선미관 · 스러스터 ·
+씰/베어링 그리스 한정)</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>대상 아님 (그리스)</t>
+        </is>
+      </c>
+      <c r="I19" s="19" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" s="17" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Shell Naturelle S2 Grease
+A600P 1.5</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>PUTERI SABAH</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Samgong · Tanktec ·
+Sangsangin · OPCO</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Klüber 자료 범위 밖</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>대상 아님 (그리스)</t>
+        </is>
+      </c>
+      <c r="I20" s="19" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="46" customHeight="1">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>CLARITY SYN EA GREASE</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>MARVEL DOVE</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>SAMGONG · A-TECH ·
+SHIN MYUNG · KTMI · ORIENTAL</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Klüber 자료 범위 밖</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>대상 아님 (그리스)</t>
+        </is>
+      </c>
+      <c r="I21" s="19" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="46" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Open Gears</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>BIO OG+</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>BU FINTAS</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>(전선 공통)</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Klüber 자료 범위 밖</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>대상 아님 (그리스)</t>
+        </is>
+      </c>
+      <c r="I22" s="19" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="46" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Grease Points
+(일반)</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>BIOMULTIS EP 2</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>BU FINTAS · SK AUDACE
+PRISM AGILITY</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Winch · Crane · Davit 등</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio AG 39-602 계열</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>대상 아님 (그리스)</t>
+        </is>
+      </c>
+      <c r="I23" s="19" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="46" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>참고 — EAL 아님</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>MOBIL Arctic EAL 32</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>MARVEL DOVE
+BU FINTAS
+SK AUDACE</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>HI-AIR KOREA</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>검토 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="168" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>▣ 읽는 법
+  · 승인 확인 = 현재 쓰는 제품과 같은 용도로 해당 장비 메이커가 Klüber EAL 을 승인한 이력이 있음 → 대체 검토 가능
+  · 확인 필요 = 장비 메이커가 Klüber 승인 목록에 없음 → Klüber 로 바꾸려면 해당 메이커 승인을 별도로 받아야 함
+  · 해당 없음 = 와이어로프 · 개방기어용 그리스로, Klüber 자료(선미관 · 스러스터 · 씰/베어링) 범위 밖
+  · SKF Marine EAL 리스트는 Simplex 선미관 씰용 「오일」 전용 목록입니다. 그리스가 미등재인 것은 결격이 아니라 대상이 아닌 것입니다.
+▣ 눈에 띄는 두 가지
+  · Rudder Carrier — 3K INDUSTRY 장비를 쓰는 3척(PUTERI SABAH · MARVEL DOVE · PRISM AGILITY)은 Klüber 가 3K 로부터 rudder shaft &amp; pump 승인을 이미 받아둔 상태입니다. 3척이 지금 서로 다른 제품(Margrease · Clarity Syn EA 0 · Tectyl ECO)을 쓰고 있어 Klüberbio LG 39-701 N 하나로 통일할 여지가 있습니다.
+  · Stern Tube — 6척 중 SK AUDACE 만 EAL(BIONEPTAN 150)입니다. 나머지 5척은 광유이며, 씰 메이커가 KEMEL · WÄRTSILÄ 라 Klüberbio RM 2-100 / RM 2-150 승인 범위 안에 들어옵니다. 다만 KEMEL 은 선박별 개별 승인이 필요합니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="A26:I26"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -682,26 +1818,26 @@
       </c>
     </row>
     <row r="5" ht="62" customHeight="1">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>TotalEnergies
 Lubmarine</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>생분해성 다목적 EP 그리스</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>AL SAKHAMAH
 BU FINTAS
@@ -709,7 +1845,7 @@
 SK AUDACE</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>Propeller Cap · Rudder Carrier ·
 Steering Gear Grease Pump ·
@@ -725,15 +1861,15 @@
       </c>
     </row>
     <row r="6" ht="62" customHeight="1">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>TotalEnergies
 Lubmarine</t>
@@ -766,31 +1902,31 @@
       </c>
     </row>
     <row r="7" ht="62" customHeight="1">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>BIO OG+</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>TotalEnergies
 Lubmarine</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>생분해성 개방기어용 그리스</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>BU FINTAS</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>General Greasing — Open Gears</t>
         </is>
@@ -802,15 +1938,15 @@
       </c>
     </row>
     <row r="8" ht="62" customHeight="1">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>BIONEPTAN HT 100</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>TotalEnergies
 Lubmarine</t>
@@ -839,36 +1975,36 @@
       </c>
     </row>
     <row r="9" ht="62" customHeight="1">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>BIONEPTAN 150</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>TotalEnergies
 Lubmarine</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>생분해성 선미관유 (ISO VG 150)</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>SK AUDACE</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>Stern Tube — Bearings &amp; Seals</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="24" t="inlineStr">
         <is>
           <t>★ 본 6척 중 유일한 Stern Tube EAL 적용. 나머지 5척은 광유
 (Melina S 30 / Atlanta Marine D 3005 / Veritas 800 Marine 30)</t>
@@ -876,16 +2012,16 @@
       </c>
     </row>
     <row r="10" ht="62" customHeight="1">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease
 A600P 1.5</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Shell</t>
         </is>
@@ -915,31 +2051,31 @@
       </c>
     </row>
     <row r="11" ht="62" customHeight="1">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>Shell Naturelle S5 Grease
 V120P 2</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>Shell</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>생분해성 다목적 그리스 (NLGI 2)</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>PUTERI SABAH</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>Propeller Bonnet / Cap Grease Filling ·
 General Grease Points</t>
@@ -952,15 +2088,15 @@
       </c>
     </row>
     <row r="12" ht="62" customHeight="1">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Chevron</t>
         </is>
@@ -990,30 +2126,30 @@
       </c>
     </row>
     <row r="13" ht="62" customHeight="1">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE 0</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>Chevron</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>합성 생분해성 그리스 (0번 주도)</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>MARVEL DOVE</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>Rudder Carrier — Grease Points</t>
         </is>
@@ -1025,15 +2161,15 @@
       </c>
     </row>
     <row r="14" ht="62" customHeight="1">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>MOBIL SHC AWARE GEAR 100</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
@@ -1053,57 +2189,57 @@
           <t>Bow Thruster 초기 충전유</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="24" t="inlineStr">
         <is>
           <t>★ 차트 본문 표에는 (EAL) 미표기 — COMMENTS 주석에만 기재</t>
         </is>
       </c>
     </row>
     <row r="15" ht="62" customHeight="1">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>MOBIL SHC AWARE GREASE EP 2</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>합성 생분해성 EP 그리스</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>SK AUDACE</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>Rudder Carrier — Grease Pump</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="24" t="inlineStr">
         <is>
           <t>★ 차트 본문 표에는 'Maker supply' 로만 기재 — COMMENTS 주석에만 제품명 명시</t>
         </is>
       </c>
     </row>
     <row r="16" ht="62" customHeight="1">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>HOUTON TECTYL G OS 5550 ECO</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Houghton (Tectyl)</t>
         </is>
@@ -1123,22 +2259,22 @@
           <t>Rudder Carrier — Grease Points</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="24" t="inlineStr">
         <is>
           <t>★ 차트 본문 표에는 'Maker supply' 로만 기재 — COMMENTS 주석에만 제품명 명시</t>
         </is>
       </c>
     </row>
     <row r="17" ht="62" customHeight="1">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Margrease EP 0</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t>확인 필요</t>
         </is>
@@ -1158,22 +2294,22 @@
           <t>Rudder Carrier — Grease Filling</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="24" t="inlineStr">
         <is>
           <t>★ 차트 주석 (B) = Shell Marine 미공급 품목. 제조사 확인 필요</t>
         </is>
       </c>
     </row>
     <row r="18" ht="62" customHeight="1">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>MOBIL Arctic EAL 32</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
@@ -1197,14 +2333,14 @@
 BU FINTAS 초기 충전유</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="24" t="inlineStr">
         <is>
           <t>★ 제품명의 'EAL' 은 상표이며 VGP 환경친화 윤활유(EAL) 아님. 밀폐 냉동회로용으로 해수 접촉부가 아님 — EAL 목록 집계 시 제외 검토 필요</t>
         </is>
       </c>
     </row>
     <row r="20" ht="118" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>▣ 확인 사항
   · 「EAL」 문자열 검색만으로는 PUTERI SABAH(Shell) · MARVEL DOVE(Chevron) 두 척이 누락됩니다. 두 차트는 EAL 을 「(VGP Compliant)」로 표기하며, 해당 제품은 Shell Naturelle 계열과 Chevron Clarity Syn EA 계열입니다.
@@ -1225,7 +2361,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1248,7 +2384,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>선박별 EAL 적용 상세 (Lubrication Chart 원문 기준)</t>
         </is>
@@ -1319,22 +2455,22 @@
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>PUTERI SABAH</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>9975521</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Shell</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>v2 / 2025-01-15</t>
         </is>
@@ -1349,7 +2485,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="G5" s="28" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -1364,7 +2500,7 @@
           <t>Samgong</t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
       <c r="K5" s="7" t="inlineStr">
         <is>
           <t>(VGP Compliant)</t>
@@ -1386,7 +2522,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -1401,7 +2537,7 @@
           <t>Samgong</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
       <c r="K6" s="7" t="inlineStr">
         <is>
           <t>(VGP Compliant)</t>
@@ -1423,7 +2559,7 @@
           <t>Towing Wire</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G7" s="28" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -1438,7 +2574,7 @@
           <t>Tanktec</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr"/>
       <c r="K7" s="7" t="inlineStr">
         <is>
           <t>(VGP Compliant)</t>
@@ -1460,7 +2596,7 @@
           <t>Open Gears &amp; Wire Ropes</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="28" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -1475,7 +2611,7 @@
           <t>Sangsangin Industry Co Ltd</t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
       <c r="K8" s="7" t="inlineStr">
         <is>
           <t>(VGP Compliant)</t>
@@ -1497,7 +2633,7 @@
           <t>Open Gears &amp; Wire Ropes</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G9" s="28" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -1512,7 +2648,7 @@
           <t>Sangsangin Industry Co Ltd</t>
         </is>
       </c>
-      <c r="J9" s="8" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
       <c r="K9" s="7" t="inlineStr">
         <is>
           <t>(VGP Compliant)</t>
@@ -1534,7 +2670,7 @@
           <t>Open Gears &amp; Wire Ropes</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G10" s="28" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -1549,7 +2685,7 @@
           <t>Sangsangin Industry Co Ltd</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr"/>
+      <c r="J10" s="6" t="inlineStr"/>
       <c r="K10" s="7" t="inlineStr">
         <is>
           <t>(VGP Compliant)</t>
@@ -1571,7 +2707,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="28" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -1586,7 +2722,7 @@
           <t>Oriental Precision (OPCO)</t>
         </is>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>HGD-062-26</t>
         </is>
@@ -1612,7 +2748,7 @@
           <t>Open Gears &amp; Wire Ropes</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G12" s="28" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -1627,7 +2763,7 @@
           <t>(전선 공통)</t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
       <c r="K12" s="7" t="inlineStr">
         <is>
           <t>(VGP Compliant)</t>
@@ -1649,7 +2785,7 @@
           <t>Grease Filling</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G13" s="28" t="inlineStr">
         <is>
           <t>Shell Naturelle S5 Grease V120P 2</t>
         </is>
@@ -1664,7 +2800,7 @@
           <t>HHI (EMD)</t>
         </is>
       </c>
-      <c r="J13" s="8" t="inlineStr"/>
+      <c r="J13" s="6" t="inlineStr"/>
       <c r="K13" s="7" t="inlineStr">
         <is>
           <t>(VGP Compliant)</t>
@@ -1686,7 +2822,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G14" s="28" t="inlineStr">
         <is>
           <t>Shell Naturelle S5 Grease V120P 2</t>
         </is>
@@ -1701,7 +2837,7 @@
           <t>(전선 공통)</t>
         </is>
       </c>
-      <c r="J14" s="8" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
       <c r="K14" s="7" t="inlineStr">
         <is>
           <t>(VGP Compliant)</t>
@@ -1709,10 +2845,10 @@
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="18" t="n"/>
-      <c r="B15" s="18" t="n"/>
-      <c r="C15" s="18" t="n"/>
-      <c r="D15" s="18" t="n"/>
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
       <c r="E15" s="7" t="inlineStr">
         <is>
           <t>Rudder Carrier</t>
@@ -1723,12 +2859,12 @@
           <t>Grease Filling</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G15" s="28" t="inlineStr">
         <is>
           <t>Margrease EP 0</t>
         </is>
       </c>
-      <c r="H15" s="19" t="inlineStr">
+      <c r="H15" s="15" t="inlineStr">
         <is>
           <t>확인 필요</t>
         </is>
@@ -1738,7 +2874,7 @@
           <t>3K Industry</t>
         </is>
       </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>MSK-602-T5M</t>
         </is>
@@ -1751,23 +2887,23 @@
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>AL SAKHAMAH</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>9986051</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>TotalEnergies
 Lubmarine</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>R3 / 2025-04-16</t>
         </is>
@@ -1782,7 +2918,7 @@
           <t>Towing Pennant</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G16" s="28" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -1797,7 +2933,7 @@
           <t>(차트상 미기재)</t>
         </is>
       </c>
-      <c r="J16" s="8" t="inlineStr"/>
+      <c r="J16" s="6" t="inlineStr"/>
       <c r="K16" s="7" t="inlineStr">
         <is>
           <t>(EAL)</t>
@@ -1819,7 +2955,7 @@
           <t>Rudder Trunk</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G17" s="28" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -1834,7 +2970,7 @@
           <t>FLUTEK</t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr"/>
+      <c r="J17" s="6" t="inlineStr"/>
       <c r="K17" s="7" t="inlineStr">
         <is>
           <t>(요약표 EAL 분류)
@@ -1843,10 +2979,10 @@
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="18" t="n"/>
-      <c r="B18" s="18" t="n"/>
-      <c r="C18" s="18" t="n"/>
-      <c r="D18" s="18" t="n"/>
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
       <c r="E18" s="7" t="inlineStr">
         <is>
           <t>Propeller Cap</t>
@@ -1857,7 +2993,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G18" s="28" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -1872,7 +3008,7 @@
           <t>SILLA METAL CO.</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr"/>
+      <c r="J18" s="6" t="inlineStr"/>
       <c r="K18" s="7" t="inlineStr">
         <is>
           <t>(EAL)</t>
@@ -1880,23 +3016,23 @@
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>BU FINTAS</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="27" t="inlineStr">
         <is>
           <t>9976824</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
         <is>
           <t>TotalEnergies
 Lubmarine</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>R2 / 2024-08-07</t>
         </is>
@@ -1911,7 +3047,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G19" s="28" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -1926,7 +3062,7 @@
           <t>SILLA METAL CO.</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr"/>
+      <c r="J19" s="6" t="inlineStr"/>
       <c r="K19" s="7" t="inlineStr">
         <is>
           <t>(EAL)</t>
@@ -1948,7 +3084,7 @@
           <t>Grease Pump</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G20" s="28" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -1963,7 +3099,7 @@
           <t>FLUTEK</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="J20" s="6" t="inlineStr">
         <is>
           <t>FE21</t>
         </is>
@@ -1989,7 +3125,7 @@
           <t>Grease Filling</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G21" s="28" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -2004,7 +3140,7 @@
           <t>MACGREGOR</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr"/>
       <c r="K21" s="7" t="inlineStr">
         <is>
           <t>(EAL)</t>
@@ -2026,7 +3162,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G22" s="28" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -2041,7 +3177,7 @@
           <t>(전선 공통)</t>
         </is>
       </c>
-      <c r="J22" s="8" t="inlineStr"/>
+      <c r="J22" s="6" t="inlineStr"/>
       <c r="K22" s="7" t="inlineStr">
         <is>
           <t>(EAL)</t>
@@ -2063,7 +3199,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G23" s="28" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -2078,7 +3214,7 @@
           <t>TANKTECH</t>
         </is>
       </c>
-      <c r="J23" s="8" t="inlineStr"/>
+      <c r="J23" s="6" t="inlineStr"/>
       <c r="K23" s="7" t="inlineStr">
         <is>
           <t>(EAL)</t>
@@ -2100,7 +3236,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G24" s="28" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -2115,7 +3251,7 @@
           <t>(전선 공통)</t>
         </is>
       </c>
-      <c r="J24" s="8" t="inlineStr"/>
+      <c r="J24" s="6" t="inlineStr"/>
       <c r="K24" s="7" t="inlineStr">
         <is>
           <t>(EAL)</t>
@@ -2137,7 +3273,7 @@
           <t>Open Gears</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G25" s="28" t="inlineStr">
         <is>
           <t>BIO OG+</t>
         </is>
@@ -2152,7 +3288,7 @@
           <t>(전선 공통)</t>
         </is>
       </c>
-      <c r="J25" s="8" t="inlineStr"/>
+      <c r="J25" s="6" t="inlineStr"/>
       <c r="K25" s="7" t="inlineStr">
         <is>
           <t>(EAL)</t>
@@ -2160,37 +3296,37 @@
       </c>
     </row>
     <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="18" t="n"/>
-      <c r="B26" s="18" t="n"/>
-      <c r="C26" s="18" t="n"/>
-      <c r="D26" s="18" t="n"/>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>(차트 COMMENTS Note 3)</t>
         </is>
       </c>
-      <c r="F26" s="20" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>초기 충전유</t>
         </is>
       </c>
-      <c r="G26" s="21" t="inlineStr">
+      <c r="G26" s="29" t="inlineStr">
         <is>
           <t>MOBIL ARCTIC EAL 32</t>
         </is>
       </c>
-      <c r="H26" s="20" t="inlineStr">
+      <c r="H26" s="13" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="I26" s="20" t="inlineStr">
+      <c r="I26" s="13" t="inlineStr">
         <is>
           <t>(차트상 미기재)</t>
         </is>
       </c>
-      <c r="J26" s="22" t="inlineStr"/>
-      <c r="K26" s="10" t="inlineStr">
+      <c r="J26" s="12" t="inlineStr"/>
+      <c r="K26" s="24" t="inlineStr">
         <is>
           <t>제품명에 EAL 포함
 ★ 냉동기 압축기용 POE 오일. 제품명의 EAL 은 상표이며 VGP 환경친화 윤활유 아님</t>
@@ -2198,22 +3334,22 @@
       </c>
     </row>
     <row r="27" ht="40" customHeight="1">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>MARVEL DOVE</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B27" s="27" t="inlineStr">
         <is>
           <t>9964182</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C27" s="27" t="inlineStr">
         <is>
           <t>Chevron</t>
         </is>
       </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="D27" s="27" t="inlineStr">
         <is>
           <t>2024-06-17</t>
         </is>
@@ -2228,7 +3364,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G27" s="28" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -2243,7 +3379,7 @@
           <t>HHI-EMD</t>
         </is>
       </c>
-      <c r="J27" s="8" t="inlineStr"/>
+      <c r="J27" s="6" t="inlineStr"/>
       <c r="K27" s="7" t="inlineStr">
         <is>
           <t>(VGP Compliant)</t>
@@ -2265,7 +3401,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="G28" s="28" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -2280,7 +3416,7 @@
           <t>SAMGONG</t>
         </is>
       </c>
-      <c r="J28" s="8" t="inlineStr">
+      <c r="J28" s="6" t="inlineStr">
         <is>
           <t>SH81731</t>
         </is>
@@ -2306,7 +3442,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="G29" s="28" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -2321,7 +3457,7 @@
           <t>SAMGONG</t>
         </is>
       </c>
-      <c r="J29" s="8" t="inlineStr">
+      <c r="J29" s="6" t="inlineStr">
         <is>
           <t>SH81731</t>
         </is>
@@ -2347,7 +3483,7 @@
           <t>Open Gears &amp; Wire Ropes</t>
         </is>
       </c>
-      <c r="G30" s="16" t="inlineStr">
+      <c r="G30" s="28" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -2362,7 +3498,7 @@
           <t>A-TECH</t>
         </is>
       </c>
-      <c r="J30" s="8" t="inlineStr"/>
+      <c r="J30" s="6" t="inlineStr"/>
       <c r="K30" s="7" t="inlineStr">
         <is>
           <t>(VGP compliant)</t>
@@ -2384,7 +3520,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="G31" s="28" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -2399,7 +3535,7 @@
           <t>SHIN MYUNG</t>
         </is>
       </c>
-      <c r="J31" s="8" t="inlineStr"/>
+      <c r="J31" s="6" t="inlineStr"/>
       <c r="K31" s="7" t="inlineStr">
         <is>
           <t>(VGP compliant)</t>
@@ -2421,7 +3557,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G32" s="16" t="inlineStr">
+      <c r="G32" s="28" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -2436,7 +3572,7 @@
           <t>SHIN MYUNG</t>
         </is>
       </c>
-      <c r="J32" s="8" t="inlineStr"/>
+      <c r="J32" s="6" t="inlineStr"/>
       <c r="K32" s="7" t="inlineStr">
         <is>
           <t>(VGP compliant)</t>
@@ -2458,7 +3594,7 @@
           <t>Towing Wire</t>
         </is>
       </c>
-      <c r="G33" s="16" t="inlineStr">
+      <c r="G33" s="28" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -2473,7 +3609,7 @@
           <t>KTMI</t>
         </is>
       </c>
-      <c r="J33" s="8" t="inlineStr"/>
+      <c r="J33" s="6" t="inlineStr"/>
       <c r="K33" s="7" t="inlineStr">
         <is>
           <t>(VGP Compliant)</t>
@@ -2495,7 +3631,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G34" s="16" t="inlineStr">
+      <c r="G34" s="28" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -2510,7 +3646,7 @@
           <t>ORIENTAL</t>
         </is>
       </c>
-      <c r="J34" s="8" t="inlineStr">
+      <c r="J34" s="6" t="inlineStr">
         <is>
           <t>HGD-062-26 / BWE-10</t>
         </is>
@@ -2537,7 +3673,7 @@
           <t>Brush Applied</t>
         </is>
       </c>
-      <c r="G35" s="16" t="inlineStr">
+      <c r="G35" s="28" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -2552,7 +3688,7 @@
           <t>(전선 공통)</t>
         </is>
       </c>
-      <c r="J35" s="8" t="inlineStr"/>
+      <c r="J35" s="6" t="inlineStr"/>
       <c r="K35" s="7" t="inlineStr">
         <is>
           <t>(VGP Compliant)</t>
@@ -2574,7 +3710,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G36" s="16" t="inlineStr">
+      <c r="G36" s="28" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE 0</t>
         </is>
@@ -2589,7 +3725,7 @@
           <t>3K INDUSTRY</t>
         </is>
       </c>
-      <c r="J36" s="8" t="inlineStr"/>
+      <c r="J36" s="6" t="inlineStr"/>
       <c r="K36" s="7" t="inlineStr">
         <is>
           <t>(VGP Compliant)</t>
@@ -2601,33 +3737,33 @@
       <c r="B37" s="17" t="n"/>
       <c r="C37" s="17" t="n"/>
       <c r="D37" s="17" t="n"/>
-      <c r="E37" s="20" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>Unit Cooler - ECR</t>
         </is>
       </c>
-      <c r="F37" s="20" t="inlineStr">
+      <c r="F37" s="13" t="inlineStr">
         <is>
           <t>Crankcase</t>
         </is>
       </c>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="G37" s="29" t="inlineStr">
         <is>
           <t>MOBIL Arctic EAL 32</t>
         </is>
       </c>
-      <c r="H37" s="20" t="inlineStr">
+      <c r="H37" s="13" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="I37" s="20" t="inlineStr">
+      <c r="I37" s="13" t="inlineStr">
         <is>
           <t>HI-AIR KOREA</t>
         </is>
       </c>
-      <c r="J37" s="22" t="inlineStr"/>
-      <c r="K37" s="10" t="inlineStr">
+      <c r="J37" s="12" t="inlineStr"/>
+      <c r="K37" s="24" t="inlineStr">
         <is>
           <t>제품명에 EAL 포함
 ★ 냉동기 압축기용 POE 오일 · Initial Fill &amp; Owner Supplied. VGP 환경친화 윤활유 아님</t>
@@ -2639,33 +3775,33 @@
       <c r="B38" s="17" t="n"/>
       <c r="C38" s="17" t="n"/>
       <c r="D38" s="17" t="n"/>
-      <c r="E38" s="20" t="inlineStr">
+      <c r="E38" s="13" t="inlineStr">
         <is>
           <t>Unit Cooler - Switch Board Room</t>
         </is>
       </c>
-      <c r="F38" s="20" t="inlineStr">
+      <c r="F38" s="13" t="inlineStr">
         <is>
           <t>Crankcase</t>
         </is>
       </c>
-      <c r="G38" s="21" t="inlineStr">
+      <c r="G38" s="29" t="inlineStr">
         <is>
           <t>MOBIL Arctic EAL 32</t>
         </is>
       </c>
-      <c r="H38" s="20" t="inlineStr">
+      <c r="H38" s="13" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="I38" s="20" t="inlineStr">
+      <c r="I38" s="13" t="inlineStr">
         <is>
           <t>HI-AIR KOREA</t>
         </is>
       </c>
-      <c r="J38" s="22" t="inlineStr"/>
-      <c r="K38" s="10" t="inlineStr">
+      <c r="J38" s="12" t="inlineStr"/>
+      <c r="K38" s="24" t="inlineStr">
         <is>
           <t>제품명에 EAL 포함
 ★ 상동 · Initial Fill &amp; Owner Supplied</t>
@@ -2673,37 +3809,37 @@
       </c>
     </row>
     <row r="39" ht="40" customHeight="1">
-      <c r="A39" s="18" t="n"/>
-      <c r="B39" s="18" t="n"/>
-      <c r="C39" s="18" t="n"/>
-      <c r="D39" s="18" t="n"/>
-      <c r="E39" s="20" t="inlineStr">
+      <c r="A39" s="10" t="n"/>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="13" t="inlineStr">
         <is>
           <t>Unit Cooler - Work Shop</t>
         </is>
       </c>
-      <c r="F39" s="20" t="inlineStr">
+      <c r="F39" s="13" t="inlineStr">
         <is>
           <t>Crankcase</t>
         </is>
       </c>
-      <c r="G39" s="21" t="inlineStr">
+      <c r="G39" s="29" t="inlineStr">
         <is>
           <t>MOBIL Arctic EAL 32</t>
         </is>
       </c>
-      <c r="H39" s="20" t="inlineStr">
+      <c r="H39" s="13" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="I39" s="20" t="inlineStr">
+      <c r="I39" s="13" t="inlineStr">
         <is>
           <t>HI-AIR KOREA</t>
         </is>
       </c>
-      <c r="J39" s="22" t="inlineStr"/>
-      <c r="K39" s="10" t="inlineStr">
+      <c r="J39" s="12" t="inlineStr"/>
+      <c r="K39" s="24" t="inlineStr">
         <is>
           <t>제품명에 EAL 포함
 ★ 상동 · Initial Fill &amp; Owner Supplied</t>
@@ -2711,23 +3847,23 @@
       </c>
     </row>
     <row r="40" ht="40" customHeight="1">
-      <c r="A40" s="14" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>PRISM AGILITY</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B40" s="27" t="inlineStr">
         <is>
           <t>9810549</t>
         </is>
       </c>
-      <c r="C40" s="15" t="inlineStr">
+      <c r="C40" s="27" t="inlineStr">
         <is>
           <t>TotalEnergies
 Lubmarine</t>
         </is>
       </c>
-      <c r="D40" s="15" t="inlineStr">
+      <c r="D40" s="27" t="inlineStr">
         <is>
           <t>R3 / 2024-01-11</t>
         </is>
@@ -2742,7 +3878,7 @@
           <t>Enclosed Gears</t>
         </is>
       </c>
-      <c r="G40" s="16" t="inlineStr">
+      <c r="G40" s="28" t="inlineStr">
         <is>
           <t>BIONEPTAN HT 100</t>
         </is>
@@ -2757,7 +3893,7 @@
           <t>KAWASAKI HEAVY INDUSTRIES (KHI)</t>
         </is>
       </c>
-      <c r="J40" s="8" t="inlineStr">
+      <c r="J40" s="6" t="inlineStr">
         <is>
           <t>KT-219B5</t>
         </is>
@@ -2783,7 +3919,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G41" s="16" t="inlineStr">
+      <c r="G41" s="28" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -2798,7 +3934,7 @@
           <t>KAWASAKI HEAVY INDUSTRIES (KHI)</t>
         </is>
       </c>
-      <c r="J41" s="8" t="inlineStr">
+      <c r="J41" s="6" t="inlineStr">
         <is>
           <t>KT-219B5</t>
         </is>
@@ -2824,7 +3960,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G42" s="16" t="inlineStr">
+      <c r="G42" s="28" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -2839,7 +3975,7 @@
           <t>HYUNDAI HEAVY INDUSTRIES (HHI)</t>
         </is>
       </c>
-      <c r="J42" s="8" t="inlineStr">
+      <c r="J42" s="6" t="inlineStr">
         <is>
           <t>FPP</t>
         </is>
@@ -2856,37 +3992,37 @@
       <c r="B43" s="17" t="n"/>
       <c r="C43" s="17" t="n"/>
       <c r="D43" s="17" t="n"/>
-      <c r="E43" s="20" t="inlineStr">
+      <c r="E43" s="13" t="inlineStr">
         <is>
           <t>Bow Thruster</t>
         </is>
       </c>
-      <c r="F43" s="20" t="inlineStr">
+      <c r="F43" s="13" t="inlineStr">
         <is>
           <t>초기 충전유 (First oil)</t>
         </is>
       </c>
-      <c r="G43" s="21" t="inlineStr">
+      <c r="G43" s="29" t="inlineStr">
         <is>
           <t>MOBIL SHC AWARE GEAR 100</t>
         </is>
       </c>
-      <c r="H43" s="20" t="inlineStr">
+      <c r="H43" s="13" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="I43" s="20" t="inlineStr">
+      <c r="I43" s="13" t="inlineStr">
         <is>
           <t>KAWASAKI HEAVY INDUSTRIES (KHI)</t>
         </is>
       </c>
-      <c r="J43" s="22" t="inlineStr">
+      <c r="J43" s="12" t="inlineStr">
         <is>
           <t>KT-219B5</t>
         </is>
       </c>
-      <c r="K43" s="10" t="inlineStr">
+      <c r="K43" s="24" t="inlineStr">
         <is>
           <t>COMMENTS Note 1
 ★ 차트 표에는 (EAL) 미표기. SHC AWARE 는 ExxonMobil 의 EAL 기어유 제품군</t>
@@ -2894,41 +4030,41 @@
       </c>
     </row>
     <row r="44" ht="40" customHeight="1">
-      <c r="A44" s="18" t="n"/>
-      <c r="B44" s="18" t="n"/>
-      <c r="C44" s="18" t="n"/>
-      <c r="D44" s="18" t="n"/>
-      <c r="E44" s="20" t="inlineStr">
+      <c r="A44" s="10" t="n"/>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="13" t="inlineStr">
         <is>
           <t>Rudder Carrier</t>
         </is>
       </c>
-      <c r="F44" s="20" t="inlineStr">
+      <c r="F44" s="13" t="inlineStr">
         <is>
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G44" s="21" t="inlineStr">
+      <c r="G44" s="29" t="inlineStr">
         <is>
           <t>HOUTON TECTYL G OS 5550 ECO</t>
         </is>
       </c>
-      <c r="H44" s="20" t="inlineStr">
+      <c r="H44" s="13" t="inlineStr">
         <is>
           <t>Houghton (Tectyl)</t>
         </is>
       </c>
-      <c r="I44" s="20" t="inlineStr">
+      <c r="I44" s="13" t="inlineStr">
         <is>
           <t>3K INDUSTRY</t>
         </is>
       </c>
-      <c r="J44" s="22" t="inlineStr">
+      <c r="J44" s="12" t="inlineStr">
         <is>
           <t>MSB-360-T6M</t>
         </is>
       </c>
-      <c r="K44" s="10" t="inlineStr">
+      <c r="K44" s="24" t="inlineStr">
         <is>
           <t>COMMENTS Note 3
 ★ 차트 표에는 'Maker supply' 로만 기재. 차트 원문 표기 'HOUTON' (Houghton 오기로 추정)</t>
@@ -2936,54 +4072,54 @@
       </c>
     </row>
     <row r="45" ht="40" customHeight="1">
-      <c r="A45" s="14" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>SK AUDACE</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B45" s="27" t="inlineStr">
         <is>
           <t>9693161</t>
         </is>
       </c>
-      <c r="C45" s="15" t="inlineStr">
+      <c r="C45" s="27" t="inlineStr">
         <is>
           <t>TotalEnergies
 Lubmarine</t>
         </is>
       </c>
-      <c r="D45" s="15" t="inlineStr">
+      <c r="D45" s="27" t="inlineStr">
         <is>
           <t>R3 / 2024-01-11</t>
         </is>
       </c>
-      <c r="E45" s="20" t="inlineStr">
+      <c r="E45" s="13" t="inlineStr">
         <is>
           <t>Stern Tube</t>
         </is>
       </c>
-      <c r="F45" s="20" t="inlineStr">
+      <c r="F45" s="13" t="inlineStr">
         <is>
           <t>Bearings &amp; Seals</t>
         </is>
       </c>
-      <c r="G45" s="21" t="inlineStr">
+      <c r="G45" s="29" t="inlineStr">
         <is>
           <t>BIONEPTAN 150</t>
         </is>
       </c>
-      <c r="H45" s="20" t="inlineStr">
+      <c r="H45" s="13" t="inlineStr">
         <is>
           <t>TotalEnergies</t>
         </is>
       </c>
-      <c r="I45" s="20" t="inlineStr">
+      <c r="I45" s="13" t="inlineStr">
         <is>
           <t>WARTSILA</t>
         </is>
       </c>
-      <c r="J45" s="22" t="inlineStr"/>
-      <c r="K45" s="10" t="inlineStr">
+      <c r="J45" s="12" t="inlineStr"/>
+      <c r="K45" s="24" t="inlineStr">
         <is>
           <t>(EAL)
 ★ 본 6척 중 유일하게 Stern Tube 에 EAL 적용 (타 5척은 광유)</t>
@@ -3005,7 +4141,7 @@
           <t>Enclosed Gears</t>
         </is>
       </c>
-      <c r="G46" s="16" t="inlineStr">
+      <c r="G46" s="28" t="inlineStr">
         <is>
           <t>BIONEPTAN HT 100</t>
         </is>
@@ -3020,7 +4156,7 @@
           <t>KHI</t>
         </is>
       </c>
-      <c r="J46" s="8" t="inlineStr"/>
+      <c r="J46" s="6" t="inlineStr"/>
       <c r="K46" s="7" t="inlineStr">
         <is>
           <t>(EAL)</t>
@@ -3042,7 +4178,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G47" s="16" t="inlineStr">
+      <c r="G47" s="28" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -3057,7 +4193,7 @@
           <t>FLUTEK</t>
         </is>
       </c>
-      <c r="J47" s="8" t="inlineStr"/>
+      <c r="J47" s="6" t="inlineStr"/>
       <c r="K47" s="7" t="inlineStr">
         <is>
           <t>(EAL)</t>
@@ -3079,7 +4215,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G48" s="16" t="inlineStr">
+      <c r="G48" s="28" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -3094,7 +4230,7 @@
           <t>ORIENTAL</t>
         </is>
       </c>
-      <c r="J48" s="8" t="inlineStr"/>
+      <c r="J48" s="6" t="inlineStr"/>
       <c r="K48" s="7" t="inlineStr">
         <is>
           <t>(EAL)</t>
@@ -3116,7 +4252,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G49" s="16" t="inlineStr">
+      <c r="G49" s="28" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -3131,7 +4267,7 @@
           <t>ORIENTAL</t>
         </is>
       </c>
-      <c r="J49" s="8" t="inlineStr"/>
+      <c r="J49" s="6" t="inlineStr"/>
       <c r="K49" s="7" t="inlineStr">
         <is>
           <t>(EAL)</t>
@@ -3153,7 +4289,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G50" s="16" t="inlineStr">
+      <c r="G50" s="28" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -3168,7 +4304,7 @@
           <t>ORIENTAL</t>
         </is>
       </c>
-      <c r="J50" s="8" t="inlineStr"/>
+      <c r="J50" s="6" t="inlineStr"/>
       <c r="K50" s="7" t="inlineStr">
         <is>
           <t>(EAL)</t>
@@ -3190,7 +4326,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G51" s="16" t="inlineStr">
+      <c r="G51" s="28" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -3205,7 +4341,7 @@
           <t>TANKTECH</t>
         </is>
       </c>
-      <c r="J51" s="8" t="inlineStr"/>
+      <c r="J51" s="6" t="inlineStr"/>
       <c r="K51" s="7" t="inlineStr">
         <is>
           <t>(EAL)</t>
@@ -3227,7 +4363,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G52" s="16" t="inlineStr">
+      <c r="G52" s="28" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -3242,7 +4378,7 @@
           <t>ORIENTAL</t>
         </is>
       </c>
-      <c r="J52" s="8" t="inlineStr"/>
+      <c r="J52" s="6" t="inlineStr"/>
       <c r="K52" s="7" t="inlineStr">
         <is>
           <t>(EAL)</t>
@@ -3264,7 +4400,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G53" s="16" t="inlineStr">
+      <c r="G53" s="28" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -3279,7 +4415,7 @@
           <t>ORIENTAL</t>
         </is>
       </c>
-      <c r="J53" s="8" t="inlineStr"/>
+      <c r="J53" s="6" t="inlineStr"/>
       <c r="K53" s="7" t="inlineStr">
         <is>
           <t>(EAL)</t>
@@ -3301,7 +4437,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G54" s="16" t="inlineStr">
+      <c r="G54" s="28" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -3316,7 +4452,7 @@
           <t>(전선 공통)</t>
         </is>
       </c>
-      <c r="J54" s="8" t="inlineStr"/>
+      <c r="J54" s="6" t="inlineStr"/>
       <c r="K54" s="7" t="inlineStr">
         <is>
           <t>(EAL)</t>
@@ -3338,7 +4474,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G55" s="16" t="inlineStr">
+      <c r="G55" s="28" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -3353,7 +4489,7 @@
           <t>ORIENTAL</t>
         </is>
       </c>
-      <c r="J55" s="8" t="inlineStr"/>
+      <c r="J55" s="6" t="inlineStr"/>
       <c r="K55" s="7" t="inlineStr">
         <is>
           <t>(EAL)</t>
@@ -3375,7 +4511,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G56" s="16" t="inlineStr">
+      <c r="G56" s="28" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -3390,7 +4526,7 @@
           <t>ORIENTAL</t>
         </is>
       </c>
-      <c r="J56" s="8" t="inlineStr"/>
+      <c r="J56" s="6" t="inlineStr"/>
       <c r="K56" s="7" t="inlineStr">
         <is>
           <t>(EAL)</t>
@@ -3412,7 +4548,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G57" s="16" t="inlineStr">
+      <c r="G57" s="28" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -3427,7 +4563,7 @@
           <t>ORIENTAL</t>
         </is>
       </c>
-      <c r="J57" s="8" t="inlineStr"/>
+      <c r="J57" s="6" t="inlineStr"/>
       <c r="K57" s="7" t="inlineStr">
         <is>
           <t>(EAL)</t>
@@ -3449,7 +4585,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G58" s="16" t="inlineStr">
+      <c r="G58" s="28" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -3464,7 +4600,7 @@
           <t>ORIENTAL</t>
         </is>
       </c>
-      <c r="J58" s="8" t="inlineStr"/>
+      <c r="J58" s="6" t="inlineStr"/>
       <c r="K58" s="7" t="inlineStr">
         <is>
           <t>(EAL)</t>
@@ -3486,7 +4622,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G59" s="16" t="inlineStr">
+      <c r="G59" s="28" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -3501,7 +4637,7 @@
           <t>ORIENTAL</t>
         </is>
       </c>
-      <c r="J59" s="8" t="inlineStr"/>
+      <c r="J59" s="6" t="inlineStr"/>
       <c r="K59" s="7" t="inlineStr">
         <is>
           <t>(EAL)</t>
@@ -3523,7 +4659,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G60" s="16" t="inlineStr">
+      <c r="G60" s="28" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -3538,7 +4674,7 @@
           <t>(전선 공통)</t>
         </is>
       </c>
-      <c r="J60" s="8" t="inlineStr"/>
+      <c r="J60" s="6" t="inlineStr"/>
       <c r="K60" s="7" t="inlineStr">
         <is>
           <t>(EAL)</t>
@@ -3550,33 +4686,33 @@
       <c r="B61" s="17" t="n"/>
       <c r="C61" s="17" t="n"/>
       <c r="D61" s="17" t="n"/>
-      <c r="E61" s="20" t="inlineStr">
+      <c r="E61" s="13" t="inlineStr">
         <is>
           <t>Rudder Carrier</t>
         </is>
       </c>
-      <c r="F61" s="20" t="inlineStr">
+      <c r="F61" s="13" t="inlineStr">
         <is>
           <t>Grease Pump</t>
         </is>
       </c>
-      <c r="G61" s="21" t="inlineStr">
+      <c r="G61" s="29" t="inlineStr">
         <is>
           <t>MOBIL SHC AWARE GREASE EP 2</t>
         </is>
       </c>
-      <c r="H61" s="20" t="inlineStr">
+      <c r="H61" s="13" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="I61" s="20" t="inlineStr">
+      <c r="I61" s="13" t="inlineStr">
         <is>
           <t>FLUTEK</t>
         </is>
       </c>
-      <c r="J61" s="22" t="inlineStr"/>
-      <c r="K61" s="10" t="inlineStr">
+      <c r="J61" s="12" t="inlineStr"/>
+      <c r="K61" s="24" t="inlineStr">
         <is>
           <t>COMMENTS Note 3
 ★ 차트 표에는 'Maker supply' 로만 기재. SHC AWARE 는 ExxonMobil 의 EAL 제품군</t>
@@ -3588,33 +4724,33 @@
       <c r="B62" s="17" t="n"/>
       <c r="C62" s="17" t="n"/>
       <c r="D62" s="17" t="n"/>
-      <c r="E62" s="20" t="inlineStr">
+      <c r="E62" s="13" t="inlineStr">
         <is>
           <t>Packaged Type Unit Cooler — ECR</t>
         </is>
       </c>
-      <c r="F62" s="20" t="inlineStr">
+      <c r="F62" s="13" t="inlineStr">
         <is>
           <t>Crankcase (Synthetic)</t>
         </is>
       </c>
-      <c r="G62" s="21" t="inlineStr">
+      <c r="G62" s="29" t="inlineStr">
         <is>
           <t>MOBIL ARCTIC EAL 32</t>
         </is>
       </c>
-      <c r="H62" s="20" t="inlineStr">
+      <c r="H62" s="13" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="I62" s="20" t="inlineStr">
+      <c r="I62" s="13" t="inlineStr">
         <is>
           <t>HI-AIR KOREA</t>
         </is>
       </c>
-      <c r="J62" s="22" t="inlineStr"/>
-      <c r="K62" s="10" t="inlineStr">
+      <c r="J62" s="12" t="inlineStr"/>
+      <c r="K62" s="24" t="inlineStr">
         <is>
           <t>COMMENTS Note 1
 ★ 냉동기 압축기용 POE 오일. 제품명의 EAL 은 상표이며 VGP 환경친화 윤활유 아님</t>
@@ -3626,33 +4762,33 @@
       <c r="B63" s="17" t="n"/>
       <c r="C63" s="17" t="n"/>
       <c r="D63" s="17" t="n"/>
-      <c r="E63" s="20" t="inlineStr">
+      <c r="E63" s="13" t="inlineStr">
         <is>
           <t>Packaged Type Unit Cooler — MSBD Room</t>
         </is>
       </c>
-      <c r="F63" s="20" t="inlineStr">
+      <c r="F63" s="13" t="inlineStr">
         <is>
           <t>Crankcase (Synthetic)</t>
         </is>
       </c>
-      <c r="G63" s="21" t="inlineStr">
+      <c r="G63" s="29" t="inlineStr">
         <is>
           <t>MOBIL ARCTIC EAL 32</t>
         </is>
       </c>
-      <c r="H63" s="20" t="inlineStr">
+      <c r="H63" s="13" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="I63" s="20" t="inlineStr">
+      <c r="I63" s="13" t="inlineStr">
         <is>
           <t>HI-AIR KOREA</t>
         </is>
       </c>
-      <c r="J63" s="22" t="inlineStr"/>
-      <c r="K63" s="10" t="inlineStr">
+      <c r="J63" s="12" t="inlineStr"/>
+      <c r="K63" s="24" t="inlineStr">
         <is>
           <t>COMMENTS Note 1
 ★ 상동</t>
@@ -3660,37 +4796,37 @@
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
-      <c r="A64" s="18" t="n"/>
-      <c r="B64" s="18" t="n"/>
-      <c r="C64" s="18" t="n"/>
-      <c r="D64" s="18" t="n"/>
-      <c r="E64" s="20" t="inlineStr">
+      <c r="A64" s="10" t="n"/>
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="13" t="inlineStr">
         <is>
           <t>Packaged Type Unit Cooler — Workshop</t>
         </is>
       </c>
-      <c r="F64" s="20" t="inlineStr">
+      <c r="F64" s="13" t="inlineStr">
         <is>
           <t>Crankcase (Synthetic)</t>
         </is>
       </c>
-      <c r="G64" s="21" t="inlineStr">
+      <c r="G64" s="29" t="inlineStr">
         <is>
           <t>MOBIL ARCTIC EAL 32</t>
         </is>
       </c>
-      <c r="H64" s="20" t="inlineStr">
+      <c r="H64" s="13" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="I64" s="20" t="inlineStr">
+      <c r="I64" s="13" t="inlineStr">
         <is>
           <t>HI-AIR KOREA</t>
         </is>
       </c>
-      <c r="J64" s="22" t="inlineStr"/>
-      <c r="K64" s="10" t="inlineStr">
+      <c r="J64" s="12" t="inlineStr"/>
+      <c r="K64" s="24" t="inlineStr">
         <is>
           <t>COMMENTS Note 1
 ★ 상동</t>
@@ -3698,7 +4834,7 @@
       </c>
     </row>
     <row r="66" ht="100" customHeight="1">
-      <c r="A66" s="12" t="inlineStr">
+      <c r="A66" s="20" t="inlineStr">
         <is>
           <t>▣ 출처
   · PUTERI SABAH — Shell Lubrication Survey, Version 2, 2025-01-15 (Vessel Code 806179)
@@ -3743,4 +4879,1353 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>Klüber EAL 승인 현황 · SKF Marine EAL 리스트 (원문 발췌)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="30" t="inlineStr">
+        <is>
+          <t>[1] Klüber EAL 승인 현황 — 6척 장비 · 씰 메이커 관련 발췌</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>장비 · 씰 메이커</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>용도</t>
+        </is>
+      </c>
+      <c r="C4" s="31" t="inlineStr">
+        <is>
+          <t>Klüber 제품</t>
+        </is>
+      </c>
+      <c r="D4" s="31" t="inlineStr">
+        <is>
+          <t>승인 내용</t>
+        </is>
+      </c>
+      <c r="E4" s="31" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+      <c r="F4" s="31" t="inlineStr">
+        <is>
+          <t>6척 해당</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>3K / Korea</t>
+        </is>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>Rudder shaft &amp; pump</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>Klüberbio LG 39-701 N</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="E5" s="33" t="inlineStr">
+        <is>
+          <t>승인현황 p.6</t>
+        </is>
+      </c>
+      <c r="F5" s="34" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Hanil Lubtec / Korea</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Rudder shaft &amp; pump</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio LG 39-701 N</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>승인현황 p.6</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="32" t="inlineStr">
+        <is>
+          <t>Kawasaki Heavy Industries / Japan</t>
+        </is>
+      </c>
+      <c r="B7" s="32" t="inlineStr">
+        <is>
+          <t>Thruster 기어유</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="inlineStr">
+        <is>
+          <t>Klüberbio EG 2-100</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="E7" s="33" t="inlineStr">
+        <is>
+          <t>승인현황 p.3 · 2018-08 업데이트 p.6</t>
+        </is>
+      </c>
+      <c r="F7" s="34" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Kawasaki Heavy Industries / Japan</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>CP propeller hub</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio EG 2-68</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>승인현황 p.5</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="32" t="inlineStr">
+        <is>
+          <t>Hyundai Heavy Industries / Korea</t>
+        </is>
+      </c>
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t>Thruster 기어유</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="inlineStr">
+        <is>
+          <t>Klüberbio EG 2-100</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="E9" s="33" t="inlineStr">
+        <is>
+          <t>승인현황 p.3 · 2018-08 업데이트 p.6</t>
+        </is>
+      </c>
+      <c r="F9" s="34" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>KTE Nakashima / Korea</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Thruster 기어유</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio EG 2-100</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>승인현황 p.3</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>HwaSeung R&amp;A / Korea</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Thruster 프로펠러축 씰</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio EG 2-68 / 100 / 150</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>승인현황 p.2</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>WÄRTSILÄ Japan (former JMT)</t>
+        </is>
+      </c>
+      <c r="B12" s="32" t="inlineStr">
+        <is>
+          <t>Stern tube 씰</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>Klüberbio RM 2-100 / RM 2-150</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="inlineStr">
+        <is>
+          <t>BIO FKM seal rings 승인</t>
+        </is>
+      </c>
+      <c r="E12" s="33" t="inlineStr">
+        <is>
+          <t>승인현황 p.1</t>
+        </is>
+      </c>
+      <c r="F12" s="34" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>WÄRTSILÄ Sweden AB (Cedervall)</t>
+        </is>
+      </c>
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>Stern tube 씰</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>Klüberbio RM 2-100 / RM 2-150</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>RM 2-150 승인 · RM 2-100 은 신형 face seal 용</t>
+        </is>
+      </c>
+      <c r="E13" s="33" t="inlineStr">
+        <is>
+          <t>승인현황 p.1</t>
+        </is>
+      </c>
+      <c r="F13" s="34" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>WÄRTSILÄ UK (Deep Sea Seals)</t>
+        </is>
+      </c>
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>Stern tube 씰</t>
+        </is>
+      </c>
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>Klüberbio RM 2-100 / RM 2-150</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>여러 씰 타입 승인 (최신 목록 별도 확인)</t>
+        </is>
+      </c>
+      <c r="E14" s="33" t="inlineStr">
+        <is>
+          <t>승인현황 p.1</t>
+        </is>
+      </c>
+      <c r="F14" s="34" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>WÄRTSILÄ Japan</t>
+        </is>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>Rudder shaft 씰</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>Klüberbio AG 39-602</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>승인현황 p.6</t>
+        </is>
+      </c>
+      <c r="F15" s="34" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>WÄRTSILÄ Propulsion / Holland</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>Thruster 기어유</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>Klüberbio EG 2-150</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="inlineStr">
+        <is>
+          <t>승인 (사전 협의 필요)</t>
+        </is>
+      </c>
+      <c r="E16" s="33" t="inlineStr">
+        <is>
+          <t>승인현황 p.4 · 업데이트 p.9</t>
+        </is>
+      </c>
+      <c r="F16" s="34" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="32" t="inlineStr">
+        <is>
+          <t>KEMEL / Japan</t>
+        </is>
+      </c>
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>Stern tube 씰</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>Klüberbio RM 2-100 / RM 2-150</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="inlineStr">
+        <is>
+          <t>승인 — 단, 선박별 개별 승인 필요</t>
+        </is>
+      </c>
+      <c r="E17" s="33" t="inlineStr">
+        <is>
+          <t>승인현황 p.1</t>
+        </is>
+      </c>
+      <c r="F17" s="34" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>KEMEL / Japan</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>Thruster 씰</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>Klüberbio EG 2-100 / EG 2-150</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="inlineStr">
+        <is>
+          <t>신형 BIO seal ring 승인</t>
+        </is>
+      </c>
+      <c r="E18" s="33" t="inlineStr">
+        <is>
+          <t>승인현황 p.2</t>
+        </is>
+      </c>
+      <c r="F18" s="34" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>SKF Marine (Simplex, 구 Blohm+Voss)</t>
+        </is>
+      </c>
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>Stern tube 씰</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>Klüberbio RM 2-100 / RM 2-150</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="inlineStr">
+        <is>
+          <t>FKM (Viton Pod · Viton Bio) 씰링 재질 승인</t>
+        </is>
+      </c>
+      <c r="E19" s="33" t="inlineStr">
+        <is>
+          <t>승인현황 p.1</t>
+        </is>
+      </c>
+      <c r="F19" s="34" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>SKF Marine (Simplex)</t>
+        </is>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>Thruster 씰</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>Klüberbio EG 2-68 / 100 / 150</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="inlineStr">
+        <is>
+          <t>FKM (Viton Pod · Viton BIO) 승인</t>
+        </is>
+      </c>
+      <c r="E20" s="33" t="inlineStr">
+        <is>
+          <t>승인현황 p.2 · 업데이트 p.12~14</t>
+        </is>
+      </c>
+      <c r="F20" s="34" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>MAN Diesel &amp; Turbo SE / Denmark</t>
+        </is>
+      </c>
+      <c r="B21" s="32" t="inlineStr">
+        <is>
+          <t>Propeller cap</t>
+        </is>
+      </c>
+      <c r="C21" s="32" t="inlineStr">
+        <is>
+          <t>Klüberbio BM 32-142 / AG 39-602 /
+LG 39-701 N</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="E21" s="33" t="inlineStr">
+        <is>
+          <t>승인현황 p.6</t>
+        </is>
+      </c>
+      <c r="F21" s="34" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>Mecklenburger Metallguss / Germany</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>Propeller cap</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="inlineStr">
+        <is>
+          <t>Klüberbio BM 32-142 / AG 39-602 /
+LG 39-701 N</t>
+        </is>
+      </c>
+      <c r="D22" s="32" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="E22" s="33" t="inlineStr">
+        <is>
+          <t>승인현황 p.6</t>
+        </is>
+      </c>
+      <c r="F22" s="34" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Sistemar Propeller / Spain</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Propeller cap</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio AG 39-602</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>승인현황 p.6</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Stone Marine / UK</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Propeller cap</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio AG 39-602</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>승인현황 p.6</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Becker Marine / Germany</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Rudder shaft</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio AG 39-602</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>승인현황 p.6</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr"/>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>[2] SKF Marine EAL 리스트 — 6척 관련 브랜드 및 Klüber 대응 후보 발췌</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B29" s="31" t="inlineStr">
+        <is>
+          <t>제품명</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="inlineStr">
+        <is>
+          <t>점도 (cSt @40℃)</t>
+        </is>
+      </c>
+      <c r="D29" s="31" t="inlineStr">
+        <is>
+          <t>분류</t>
+        </is>
+      </c>
+      <c r="E29" s="31" t="inlineStr">
+        <is>
+          <t>씰링 재질</t>
+        </is>
+      </c>
+      <c r="F29" s="31" t="inlineStr">
+        <is>
+          <t>6척 사용 여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="33" t="inlineStr">
+        <is>
+          <t>Total Lubmarine</t>
+        </is>
+      </c>
+      <c r="B30" s="32" t="inlineStr">
+        <is>
+          <t>Bioneptan 150</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D30" s="33" t="inlineStr">
+        <is>
+          <t>Sterntube Oil</t>
+        </is>
+      </c>
+      <c r="E30" s="33" t="inlineStr">
+        <is>
+          <t>FKM Pod, FKM Bio</t>
+        </is>
+      </c>
+      <c r="F30" s="35" t="inlineStr">
+        <is>
+          <t>SK AUDACE 사용 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="33" t="inlineStr">
+        <is>
+          <t>Total Lubmarine</t>
+        </is>
+      </c>
+      <c r="B31" s="32" t="inlineStr">
+        <is>
+          <t>Bioneptan HT 100</t>
+        </is>
+      </c>
+      <c r="C31" s="33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D31" s="33" t="inlineStr">
+        <is>
+          <t>Multipurpose Oil</t>
+        </is>
+      </c>
+      <c r="E31" s="33" t="inlineStr">
+        <is>
+          <t>FKM Pod, FKM Bio</t>
+        </is>
+      </c>
+      <c r="F31" s="35" t="inlineStr">
+        <is>
+          <t>PRISM AGILITY · SK AUDACE 사용 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Total Lubmarine</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Bioneptan 100</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Sterntube Oil</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>FKM Pod, FKM Bio</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Total Lubmarine</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Carter Bio 150</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Sterntube Oil</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>FKM Pod, FKM Bio</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Total Lubmarine</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Biohydran TMP 100</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Hydraulic Oil</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>FKM Pod, FKM Bio</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="33" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="B35" s="32" t="inlineStr">
+        <is>
+          <t>Mobil SHC Aware Gear 100</t>
+        </is>
+      </c>
+      <c r="C35" s="33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D35" s="33" t="inlineStr">
+        <is>
+          <t>Gear Oil</t>
+        </is>
+      </c>
+      <c r="E35" s="33" t="inlineStr">
+        <is>
+          <t>FKM Pod, FKM Bio</t>
+        </is>
+      </c>
+      <c r="F35" s="35" t="inlineStr">
+        <is>
+          <t>PRISM AGILITY 사용 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Mobil SHC Aware Gear 68</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Gear Oil</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>FKM Pod, FKM Bio</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Mobil SHC Aware Gear 150</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Gear Oil</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>FKM Pod, FKM Bio</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Mobil SHC Aware ST 100</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Sterntube Oil</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>FKM Pod, FKM Bio</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>— (SKF 협의 필요 품목)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Naturelle S4 Stern Tube Fluid 100</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Sterntube Oil</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>FKM Pod, FKM Bio</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Naturelle S4 Gear Fluid 68 / 100 / 150</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>68 / 100 / 150</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Gear Oil</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>FKM Pod, FKM Bio</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Clarity Synthetic EA Gear Oil 100 / 150</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>100 / 150</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Gear Oil</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>FKM Pod, FKM Bio</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Clarity Synthetic EA Hydraulic Oil 68 / 100</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>68 / 100</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>Hydraulic Oil</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>FKM Pod, FKM Bio</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Klüber</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio RM 2-100</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Sterntube Oil</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>FKM Pod, FKM Bio</t>
+        </is>
+      </c>
+      <c r="F43" s="36" t="inlineStr">
+        <is>
+          <t>대응 후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Klüber</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio RM 2-150</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Sterntube Oil</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>FKM Pod, FKM Bio</t>
+        </is>
+      </c>
+      <c r="F44" s="36" t="inlineStr">
+        <is>
+          <t>대응 후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Klüber</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio RM 8-100</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Sterntube Oil</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>FKM Pod, FKM Bio</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Klüber</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio EG 2-68 / 100 / 150</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>68 / 100 / 150</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Gear Oil</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>FKM Pod, FKM Bio</t>
+        </is>
+      </c>
+      <c r="F46" s="36" t="inlineStr">
+        <is>
+          <t>대응 후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Klüber</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Klüberbio LR 9-46 / 68</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>46 / 68</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Hydraulic Oil</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>FKM Pod, FKM Bio</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="130" customHeight="1">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>▣ 출처 및 단서
+  · Klüber EAL Approval Status, 2018-02-13 (GATE-MOG / Dirk Fabry, 6p)
+  · Update Klüberbio EG 2 oils APPROVALS, 2018-08-28 v4.1 — Wilhelmsen Ships Service Singapore 교육자료
+  · SKF Marine 「Find the right EAL」 리스트 (출력일 2026-08-14, SKF Marine GmbH 5p)
+  · Klüber 자료는 2018년 기준입니다. 실제 제안 전 최신 승인 목록을 Klüber 및 해당 장비 메이커에 재확인하십시오.
+  · SKF 리스트는 Simplex 선미관 씰 시스템용 「오일」 전용이며, 중간축 베어링 · 스러스트 베어링 · 기어 · 클러치에는 적용되지 않습니다.
+  · SKF 원문 주의 : 「모든 bio oil 이 EAL 인 것은 아니다」 — EAL 여부는 오일 제조사의 책임이며 SKF 는 제조사 정보에 의존합니다.
+  · EAL 사용 시 Simplex 립링 씰은 FKM Pod 또는 FKM Bio 재질이어야 합니다. 기존 씰 재질이 다르면 씰 교체가 필요합니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A28:F28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/EAL_제품_메이커_정리_6척.xlsx
+++ b/EAL_제품_메이커_정리_6척.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,7 +58,11 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <b val="1"/>
+      <color rgb="001F7A3D"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <color rgb="00C00000"/>
       <sz val="9"/>
     </font>
@@ -78,6 +82,12 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
       <sz val="9"/>
     </font>
     <font>
@@ -142,12 +152,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F7F9FC"/>
+        <fgColor rgb="00EAF4EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4E4"/>
+        <fgColor rgb="00F7F9FC"/>
       </patternFill>
     </fill>
     <fill>
@@ -162,12 +172,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
+        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF4EC"/>
+        <fgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -230,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -241,7 +251,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -253,87 +263,93 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1760,8 +1776,8 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1813,11 +1829,11 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="62" customHeight="1">
+          <t>Klüber 대응 품목 (Wilhelmsen 공급)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="92" customHeight="1">
       <c r="A5" s="21" t="n">
         <v>1</v>
       </c>
@@ -1854,13 +1870,20 @@
 Emergency Towing · General Greasing</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>4개 선박 · 총 15개 부위. 본 6척 중 최다 적용 EAL 제품</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="62" customHeight="1">
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>● Propeller Cap 용
+   210016  KLÜBERBIO BM 32-142 25 KG
+● Rudder Carrier / Shaft·Pump 용
+   210028  KLÜBERBIO LG 39-701 N 18 KG
+   210072  KLÜBERBIO LG 39-701 N 180 KG
+● 일반 Grease Point · 씰 용
+   210077  KLÜBERBIO AG 39-602 N 25 KG
+   210078  KLÜBERBIO AG 39-602 N 180 KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="92" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
@@ -1895,13 +1918,16 @@
 General Greasing</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>3개 선박 · 총 10개 부위</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="62" customHeight="1">
+      <c r="G6" s="25" t="inlineStr">
+        <is>
+          <t>직접 대응 품목 미확인
+후보 (용도 확인 필요)
+   210068  KLÜBERBIO AM 92-142 25 KG
+   210021  KLÜBERBIO AM 92-142 180 KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="92" customHeight="1">
       <c r="A7" s="21" t="n">
         <v>3</v>
       </c>
@@ -1931,13 +1957,18 @@
           <t>General Greasing — Open Gears</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>1개 선박 · 1개 부위</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="62" customHeight="1">
+      <c r="G7" s="25" t="inlineStr">
+        <is>
+          <t>직접 대응 품목 미확인
+후보 (용도 확인 필요)
+   210098  KLÜBERBIO GE 32-681 25 KG
+   210094  KLÜBERBIO GE 32-681 180 KG
+※ 210060 GRAFLOSCON C-SG 0 ULTRA 는
+   개방기어용이나 BIO 계열 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="92" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
@@ -1968,13 +1999,15 @@
           <t>Bow Thruster — Enclosed Gears</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>2개 선박 · 총 2개 부위</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="62" customHeight="1">
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>210004  KLÜBERBIO EG 2-100 200 LTR
+→ 동일 점도(VG 100) 스러스터 기어유
+→ KHI 승인 · SKF EAL 리스트 등재</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="92" customHeight="1">
       <c r="A9" s="21" t="n">
         <v>5</v>
       </c>
@@ -2006,12 +2039,14 @@
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t>★ 본 6척 중 유일한 Stern Tube EAL 적용. 나머지 5척은 광유
-(Melina S 30 / Atlanta Marine D 3005 / Veritas 800 Marine 30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="62" customHeight="1">
+          <t>210056  KLÜBERBIO RM 2-150 200 LTR
+→ 동일 점도(VG 150) 선미관유
+→ Wärtsilä 승인 · SKF EAL 리스트 등재
+※ VG 100 필요 시 210012 RM 2-100</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="92" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>6</v>
       </c>
@@ -2044,13 +2079,16 @@
 General Lubrication</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>구 제품명 : Naturelle S2 Wire Rope Lubricant A (차트 부록 기재)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="62" customHeight="1">
+      <c r="G10" s="25" t="inlineStr">
+        <is>
+          <t>직접 대응 품목 미확인
+후보 (용도 확인 필요)
+   210068  KLÜBERBIO AM 92-142 25 KG
+   210021  KLÜBERBIO AM 92-142 180 KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="92" customHeight="1">
       <c r="A11" s="21" t="n">
         <v>7</v>
       </c>
@@ -2081,13 +2119,17 @@
 General Grease Points</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>1개 선박 · 2개 부위</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="62" customHeight="1">
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>210016  KLÜBERBIO BM 32-142 25 KG
+→ Propeller Cap 용 (MAN D&amp;T · MMG 승인)
+일반 Grease Point 겸용 시
+   210077  KLÜBERBIO AG 39-602 N 25 KG
+   210078  KLÜBERBIO AG 39-602 N 180 KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="92" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>8</v>
       </c>
@@ -2119,13 +2161,18 @@
 Open Gears (Brush Applied)</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>1개 선박 · 9개 부위</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="62" customHeight="1">
+      <c r="G12" s="25" t="inlineStr">
+        <is>
+          <t>● Propeller Bonnet 용
+   210016  KLÜBERBIO BM 32-142 25 KG
+● Wire Ropes · Open Gears 용
+   직접 대응 품목 미확인
+   후보 210068 / 210021 AM 92-142
+        210098 / 210094 GE 32-681</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="92" customHeight="1">
       <c r="A13" s="21" t="n">
         <v>9</v>
       </c>
@@ -2154,13 +2201,16 @@
           <t>Rudder Carrier — Grease Points</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>Rudder Carrier 전용으로 별도 지정</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="62" customHeight="1">
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>210028  KLÜBERBIO LG 39-701 N 18 KG
+210072  KLÜBERBIO LG 39-701 N 180 KG
+→ 3K / Korea rudder shaft &amp; pump 승인
+※ 현재품 0번 주도 — 주도 등급 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="92" customHeight="1">
       <c r="A14" s="6" t="n">
         <v>10</v>
       </c>
@@ -2191,11 +2241,13 @@
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t>★ 차트 본문 표에는 (EAL) 미표기 — COMMENTS 주석에만 기재</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="62" customHeight="1">
+          <t>210004  KLÜBERBIO EG 2-100 200 LTR
+→ 동일 점도(VG 100) 스러스터 기어유
+→ KHI 승인 · SKF EAL 리스트 등재</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="92" customHeight="1">
       <c r="A15" s="21" t="n">
         <v>11</v>
       </c>
@@ -2224,13 +2276,16 @@
           <t>Rudder Carrier — Grease Pump</t>
         </is>
       </c>
-      <c r="G15" s="24" t="inlineStr">
-        <is>
-          <t>★ 차트 본문 표에는 'Maker supply' 로만 기재 — COMMENTS 주석에만 제품명 명시</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="62" customHeight="1">
+      <c r="G15" s="25" t="inlineStr">
+        <is>
+          <t>210028  KLÜBERBIO LG 39-701 N 18 KG
+210072  KLÜBERBIO LG 39-701 N 180 KG
+또는 210077 / 210078 AG 39-602 N
+※ FLUTEK 승인 이력 없음 — 개별 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="92" customHeight="1">
       <c r="A16" s="6" t="n">
         <v>12</v>
       </c>
@@ -2261,11 +2316,13 @@
       </c>
       <c r="G16" s="24" t="inlineStr">
         <is>
-          <t>★ 차트 본문 표에는 'Maker supply' 로만 기재 — COMMENTS 주석에만 제품명 명시</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="62" customHeight="1">
+          <t>210028  KLÜBERBIO LG 39-701 N 18 KG
+210072  KLÜBERBIO LG 39-701 N 180 KG
+→ 3K / Korea rudder shaft &amp; pump 승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="92" customHeight="1">
       <c r="A17" s="6" t="n">
         <v>13</v>
       </c>
@@ -2274,7 +2331,7 @@
           <t>Margrease EP 0</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>확인 필요</t>
         </is>
@@ -2296,11 +2353,14 @@
       </c>
       <c r="G17" s="24" t="inlineStr">
         <is>
-          <t>★ 차트 주석 (B) = Shell Marine 미공급 품목. 제조사 확인 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="62" customHeight="1">
+          <t>210028  KLÜBERBIO LG 39-701 N 18 KG
+210072  KLÜBERBIO LG 39-701 N 180 KG
+→ 3K / Korea rudder shaft &amp; pump 승인
+※ 현재품 0번 주도 — 주도 등급 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="92" customHeight="1">
       <c r="A18" s="6" t="n">
         <v>14</v>
       </c>
@@ -2333,21 +2393,27 @@
 BU FINTAS 초기 충전유</t>
         </is>
       </c>
-      <c r="G18" s="24" t="inlineStr">
-        <is>
-          <t>★ 제품명의 'EAL' 은 상표이며 VGP 환경친화 윤활유(EAL) 아님. 밀폐 냉동회로용으로 해수 접촉부가 아님 — EAL 목록 집계 시 제외 검토 필요</t>
+      <c r="G18" s="25" t="inlineStr">
+        <is>
+          <t>210170  KLÜBER SUMMIT RPE 32 (PAIL 20 LTR)
+210175  KLÜBER SUMMIT RPE 32 (DRUM 200 LTR)
+→ 동일 점도(VG 32) 냉동기 압축기유
+※ 양쪽 모두 EAL 아님. 냉매 적합성 확인 필요</t>
         </is>
       </c>
     </row>
     <row r="20" ht="118" customHeight="1">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>▣ 확인 사항
-  · 「EAL」 문자열 검색만으로는 PUTERI SABAH(Shell) · MARVEL DOVE(Chevron) 두 척이 누락됩니다. 두 차트는 EAL 을 「(VGP Compliant)」로 표기하며, 해당 제품은 Shell Naturelle 계열과 Chevron Clarity Syn EA 계열입니다.
-  · MOBIL Arctic EAL 32 는 제품명에 EAL 이 들어가지만 냉동기 압축기용 POE 오일입니다. 해수 접촉부(oil-to-sea interface)가 아니므로 VGP 상 EAL 과 성격이 다릅니다 — 집계 목적에 따라 제외를 검토하십시오.
-  · MOBIL SHC AWARE GEAR 100 과 HOUTON TECTYL G OS 5550 ECO 는 PRISM AGILITY 차트 본문 표가 아닌 COMMENTS 주석에만 있어 표 검색으로는 잡히지 않습니다.
-  · Margrease EP 0 (PUTERI SABAH Rudder Carrier) 는 VGP Compliant 로 지정되었으나 Shell 미공급 품목이라 제조사가 차트에 없습니다.
-  · 노란색 셀 = 원문에서 확인되지 않아 별도 확인이 필요한 항목입니다.</t>
+          <t>▣ Klüber 대응 품목 읽는 법
+  · 초록색 = 용도 · 점도 · 장비 메이커 승인까지 맞아떨어지는 대응 품목
+  · 노란색 = 대응 품목은 있으나 별도 확인이 필요 (용도 미확인 / 장비 메이커 승인 이력 없음 / 주도 등급 상이)
+  · 품목번호는 Wilhelmsen 공급 Klüber 품목 리스트 기준이며, 포장 단위(25 KG · 180 KG · 200 LTR 등)까지 표기했습니다.
+  · 그리스는 하나의 현재 제품이 여러 부위에 쓰이는 경우가 많아, Klüber 쪽은 부위별로 품목이 갈립니다. 「● 부위 → 품목」 형태로 나눠 적었습니다.
+▣ 대응 품목이 확정되지 않은 두 용도
+  · 와이어로프 점착 그리스 (BIOADHESIVE PLUS · Naturelle S2 Grease · Clarity Syn EA Grease) 와 개방기어 그리스 (BIO OG+) 는 Klüber 승인 자료 · SKF 리스트 어느 쪽에도 해당 용도가 없습니다. 품목 리스트상 KLÜBERBIO AM 92-142 와 GE 32-681 이 후보이나, 두 품목의 용도는 제공된 자료로 확인되지 않아 Klüber 확인이 필요합니다.
+  · MOBIL Arctic EAL 32 는 냉동기 압축기유로 EAL 이 아닙니다. 대응품으로 적은 KLÜBER SUMMIT RPE 32 도 EAL 이 아니며, 점도(VG 32)만 같습니다. 냉매 적합성은 별도 확인이 필요합니다.
+  · Klüber 승인 근거는 2018년 자료 기준입니다. 상세 근거는 'Klüber·SKF 참조' 시트를 보십시오.</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2450,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>선박별 EAL 적용 상세 (Lubrication Chart 원문 기준)</t>
         </is>
@@ -2460,17 +2526,17 @@
           <t>PUTERI SABAH</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>9975521</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>Shell</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>v2 / 2025-01-15</t>
         </is>
@@ -2485,7 +2551,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G5" s="28" t="inlineStr">
+      <c r="G5" s="29" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -2522,7 +2588,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G6" s="28" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -2559,7 +2625,7 @@
           <t>Towing Wire</t>
         </is>
       </c>
-      <c r="G7" s="28" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -2596,7 +2662,7 @@
           <t>Open Gears &amp; Wire Ropes</t>
         </is>
       </c>
-      <c r="G8" s="28" t="inlineStr">
+      <c r="G8" s="29" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -2633,7 +2699,7 @@
           <t>Open Gears &amp; Wire Ropes</t>
         </is>
       </c>
-      <c r="G9" s="28" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -2670,7 +2736,7 @@
           <t>Open Gears &amp; Wire Ropes</t>
         </is>
       </c>
-      <c r="G10" s="28" t="inlineStr">
+      <c r="G10" s="29" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -2707,7 +2773,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G11" s="28" t="inlineStr">
+      <c r="G11" s="29" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -2748,7 +2814,7 @@
           <t>Open Gears &amp; Wire Ropes</t>
         </is>
       </c>
-      <c r="G12" s="28" t="inlineStr">
+      <c r="G12" s="29" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -2785,7 +2851,7 @@
           <t>Grease Filling</t>
         </is>
       </c>
-      <c r="G13" s="28" t="inlineStr">
+      <c r="G13" s="29" t="inlineStr">
         <is>
           <t>Shell Naturelle S5 Grease V120P 2</t>
         </is>
@@ -2822,7 +2888,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G14" s="28" t="inlineStr">
+      <c r="G14" s="29" t="inlineStr">
         <is>
           <t>Shell Naturelle S5 Grease V120P 2</t>
         </is>
@@ -2859,7 +2925,7 @@
           <t>Grease Filling</t>
         </is>
       </c>
-      <c r="G15" s="28" t="inlineStr">
+      <c r="G15" s="29" t="inlineStr">
         <is>
           <t>Margrease EP 0</t>
         </is>
@@ -2892,18 +2958,18 @@
           <t>AL SAKHAMAH</t>
         </is>
       </c>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>9986051</t>
         </is>
       </c>
-      <c r="C16" s="27" t="inlineStr">
+      <c r="C16" s="28" t="inlineStr">
         <is>
           <t>TotalEnergies
 Lubmarine</t>
         </is>
       </c>
-      <c r="D16" s="27" t="inlineStr">
+      <c r="D16" s="28" t="inlineStr">
         <is>
           <t>R3 / 2025-04-16</t>
         </is>
@@ -2918,7 +2984,7 @@
           <t>Towing Pennant</t>
         </is>
       </c>
-      <c r="G16" s="28" t="inlineStr">
+      <c r="G16" s="29" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -2955,7 +3021,7 @@
           <t>Rudder Trunk</t>
         </is>
       </c>
-      <c r="G17" s="28" t="inlineStr">
+      <c r="G17" s="29" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -2993,7 +3059,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="G18" s="28" t="inlineStr">
+      <c r="G18" s="29" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -3021,18 +3087,18 @@
           <t>BU FINTAS</t>
         </is>
       </c>
-      <c r="B19" s="27" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>9976824</t>
         </is>
       </c>
-      <c r="C19" s="27" t="inlineStr">
+      <c r="C19" s="28" t="inlineStr">
         <is>
           <t>TotalEnergies
 Lubmarine</t>
         </is>
       </c>
-      <c r="D19" s="27" t="inlineStr">
+      <c r="D19" s="28" t="inlineStr">
         <is>
           <t>R2 / 2024-08-07</t>
         </is>
@@ -3047,7 +3113,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="G19" s="28" t="inlineStr">
+      <c r="G19" s="29" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -3084,7 +3150,7 @@
           <t>Grease Pump</t>
         </is>
       </c>
-      <c r="G20" s="28" t="inlineStr">
+      <c r="G20" s="29" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -3125,7 +3191,7 @@
           <t>Grease Filling</t>
         </is>
       </c>
-      <c r="G21" s="28" t="inlineStr">
+      <c r="G21" s="29" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -3162,7 +3228,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G22" s="28" t="inlineStr">
+      <c r="G22" s="29" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -3199,7 +3265,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G23" s="28" t="inlineStr">
+      <c r="G23" s="29" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -3236,7 +3302,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G24" s="28" t="inlineStr">
+      <c r="G24" s="29" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -3273,7 +3339,7 @@
           <t>Open Gears</t>
         </is>
       </c>
-      <c r="G25" s="28" t="inlineStr">
+      <c r="G25" s="29" t="inlineStr">
         <is>
           <t>BIO OG+</t>
         </is>
@@ -3310,7 +3376,7 @@
           <t>초기 충전유</t>
         </is>
       </c>
-      <c r="G26" s="29" t="inlineStr">
+      <c r="G26" s="30" t="inlineStr">
         <is>
           <t>MOBIL ARCTIC EAL 32</t>
         </is>
@@ -3326,7 +3392,7 @@
         </is>
       </c>
       <c r="J26" s="12" t="inlineStr"/>
-      <c r="K26" s="24" t="inlineStr">
+      <c r="K26" s="31" t="inlineStr">
         <is>
           <t>제품명에 EAL 포함
 ★ 냉동기 압축기용 POE 오일. 제품명의 EAL 은 상표이며 VGP 환경친화 윤활유 아님</t>
@@ -3339,17 +3405,17 @@
           <t>MARVEL DOVE</t>
         </is>
       </c>
-      <c r="B27" s="27" t="inlineStr">
+      <c r="B27" s="28" t="inlineStr">
         <is>
           <t>9964182</t>
         </is>
       </c>
-      <c r="C27" s="27" t="inlineStr">
+      <c r="C27" s="28" t="inlineStr">
         <is>
           <t>Chevron</t>
         </is>
       </c>
-      <c r="D27" s="27" t="inlineStr">
+      <c r="D27" s="28" t="inlineStr">
         <is>
           <t>2024-06-17</t>
         </is>
@@ -3364,7 +3430,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G27" s="28" t="inlineStr">
+      <c r="G27" s="29" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -3401,7 +3467,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G28" s="28" t="inlineStr">
+      <c r="G28" s="29" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -3442,7 +3508,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G29" s="28" t="inlineStr">
+      <c r="G29" s="29" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -3483,7 +3549,7 @@
           <t>Open Gears &amp; Wire Ropes</t>
         </is>
       </c>
-      <c r="G30" s="28" t="inlineStr">
+      <c r="G30" s="29" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -3520,7 +3586,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G31" s="28" t="inlineStr">
+      <c r="G31" s="29" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -3557,7 +3623,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G32" s="28" t="inlineStr">
+      <c r="G32" s="29" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -3594,7 +3660,7 @@
           <t>Towing Wire</t>
         </is>
       </c>
-      <c r="G33" s="28" t="inlineStr">
+      <c r="G33" s="29" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -3631,7 +3697,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G34" s="28" t="inlineStr">
+      <c r="G34" s="29" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -3673,7 +3739,7 @@
           <t>Brush Applied</t>
         </is>
       </c>
-      <c r="G35" s="28" t="inlineStr">
+      <c r="G35" s="29" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -3710,7 +3776,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G36" s="28" t="inlineStr">
+      <c r="G36" s="29" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE 0</t>
         </is>
@@ -3747,7 +3813,7 @@
           <t>Crankcase</t>
         </is>
       </c>
-      <c r="G37" s="29" t="inlineStr">
+      <c r="G37" s="30" t="inlineStr">
         <is>
           <t>MOBIL Arctic EAL 32</t>
         </is>
@@ -3763,7 +3829,7 @@
         </is>
       </c>
       <c r="J37" s="12" t="inlineStr"/>
-      <c r="K37" s="24" t="inlineStr">
+      <c r="K37" s="31" t="inlineStr">
         <is>
           <t>제품명에 EAL 포함
 ★ 냉동기 압축기용 POE 오일 · Initial Fill &amp; Owner Supplied. VGP 환경친화 윤활유 아님</t>
@@ -3785,7 +3851,7 @@
           <t>Crankcase</t>
         </is>
       </c>
-      <c r="G38" s="29" t="inlineStr">
+      <c r="G38" s="30" t="inlineStr">
         <is>
           <t>MOBIL Arctic EAL 32</t>
         </is>
@@ -3801,7 +3867,7 @@
         </is>
       </c>
       <c r="J38" s="12" t="inlineStr"/>
-      <c r="K38" s="24" t="inlineStr">
+      <c r="K38" s="31" t="inlineStr">
         <is>
           <t>제품명에 EAL 포함
 ★ 상동 · Initial Fill &amp; Owner Supplied</t>
@@ -3823,7 +3889,7 @@
           <t>Crankcase</t>
         </is>
       </c>
-      <c r="G39" s="29" t="inlineStr">
+      <c r="G39" s="30" t="inlineStr">
         <is>
           <t>MOBIL Arctic EAL 32</t>
         </is>
@@ -3839,7 +3905,7 @@
         </is>
       </c>
       <c r="J39" s="12" t="inlineStr"/>
-      <c r="K39" s="24" t="inlineStr">
+      <c r="K39" s="31" t="inlineStr">
         <is>
           <t>제품명에 EAL 포함
 ★ 상동 · Initial Fill &amp; Owner Supplied</t>
@@ -3852,18 +3918,18 @@
           <t>PRISM AGILITY</t>
         </is>
       </c>
-      <c r="B40" s="27" t="inlineStr">
+      <c r="B40" s="28" t="inlineStr">
         <is>
           <t>9810549</t>
         </is>
       </c>
-      <c r="C40" s="27" t="inlineStr">
+      <c r="C40" s="28" t="inlineStr">
         <is>
           <t>TotalEnergies
 Lubmarine</t>
         </is>
       </c>
-      <c r="D40" s="27" t="inlineStr">
+      <c r="D40" s="28" t="inlineStr">
         <is>
           <t>R3 / 2024-01-11</t>
         </is>
@@ -3878,7 +3944,7 @@
           <t>Enclosed Gears</t>
         </is>
       </c>
-      <c r="G40" s="28" t="inlineStr">
+      <c r="G40" s="29" t="inlineStr">
         <is>
           <t>BIONEPTAN HT 100</t>
         </is>
@@ -3919,7 +3985,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G41" s="28" t="inlineStr">
+      <c r="G41" s="29" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -3960,7 +4026,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G42" s="28" t="inlineStr">
+      <c r="G42" s="29" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -4002,7 +4068,7 @@
           <t>초기 충전유 (First oil)</t>
         </is>
       </c>
-      <c r="G43" s="29" t="inlineStr">
+      <c r="G43" s="30" t="inlineStr">
         <is>
           <t>MOBIL SHC AWARE GEAR 100</t>
         </is>
@@ -4022,7 +4088,7 @@
           <t>KT-219B5</t>
         </is>
       </c>
-      <c r="K43" s="24" t="inlineStr">
+      <c r="K43" s="31" t="inlineStr">
         <is>
           <t>COMMENTS Note 1
 ★ 차트 표에는 (EAL) 미표기. SHC AWARE 는 ExxonMobil 의 EAL 기어유 제품군</t>
@@ -4044,7 +4110,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G44" s="29" t="inlineStr">
+      <c r="G44" s="30" t="inlineStr">
         <is>
           <t>HOUTON TECTYL G OS 5550 ECO</t>
         </is>
@@ -4064,7 +4130,7 @@
           <t>MSB-360-T6M</t>
         </is>
       </c>
-      <c r="K44" s="24" t="inlineStr">
+      <c r="K44" s="31" t="inlineStr">
         <is>
           <t>COMMENTS Note 3
 ★ 차트 표에는 'Maker supply' 로만 기재. 차트 원문 표기 'HOUTON' (Houghton 오기로 추정)</t>
@@ -4077,18 +4143,18 @@
           <t>SK AUDACE</t>
         </is>
       </c>
-      <c r="B45" s="27" t="inlineStr">
+      <c r="B45" s="28" t="inlineStr">
         <is>
           <t>9693161</t>
         </is>
       </c>
-      <c r="C45" s="27" t="inlineStr">
+      <c r="C45" s="28" t="inlineStr">
         <is>
           <t>TotalEnergies
 Lubmarine</t>
         </is>
       </c>
-      <c r="D45" s="27" t="inlineStr">
+      <c r="D45" s="28" t="inlineStr">
         <is>
           <t>R3 / 2024-01-11</t>
         </is>
@@ -4103,7 +4169,7 @@
           <t>Bearings &amp; Seals</t>
         </is>
       </c>
-      <c r="G45" s="29" t="inlineStr">
+      <c r="G45" s="30" t="inlineStr">
         <is>
           <t>BIONEPTAN 150</t>
         </is>
@@ -4119,7 +4185,7 @@
         </is>
       </c>
       <c r="J45" s="12" t="inlineStr"/>
-      <c r="K45" s="24" t="inlineStr">
+      <c r="K45" s="31" t="inlineStr">
         <is>
           <t>(EAL)
 ★ 본 6척 중 유일하게 Stern Tube 에 EAL 적용 (타 5척은 광유)</t>
@@ -4141,7 +4207,7 @@
           <t>Enclosed Gears</t>
         </is>
       </c>
-      <c r="G46" s="28" t="inlineStr">
+      <c r="G46" s="29" t="inlineStr">
         <is>
           <t>BIONEPTAN HT 100</t>
         </is>
@@ -4178,7 +4244,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G47" s="28" t="inlineStr">
+      <c r="G47" s="29" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -4215,7 +4281,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G48" s="28" t="inlineStr">
+      <c r="G48" s="29" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -4252,7 +4318,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G49" s="28" t="inlineStr">
+      <c r="G49" s="29" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -4289,7 +4355,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G50" s="28" t="inlineStr">
+      <c r="G50" s="29" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -4326,7 +4392,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G51" s="28" t="inlineStr">
+      <c r="G51" s="29" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -4363,7 +4429,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G52" s="28" t="inlineStr">
+      <c r="G52" s="29" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -4400,7 +4466,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G53" s="28" t="inlineStr">
+      <c r="G53" s="29" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -4437,7 +4503,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G54" s="28" t="inlineStr">
+      <c r="G54" s="29" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -4474,7 +4540,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G55" s="28" t="inlineStr">
+      <c r="G55" s="29" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -4511,7 +4577,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G56" s="28" t="inlineStr">
+      <c r="G56" s="29" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -4548,7 +4614,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G57" s="28" t="inlineStr">
+      <c r="G57" s="29" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -4585,7 +4651,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G58" s="28" t="inlineStr">
+      <c r="G58" s="29" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -4622,7 +4688,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G59" s="28" t="inlineStr">
+      <c r="G59" s="29" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -4659,7 +4725,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G60" s="28" t="inlineStr">
+      <c r="G60" s="29" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -4696,7 +4762,7 @@
           <t>Grease Pump</t>
         </is>
       </c>
-      <c r="G61" s="29" t="inlineStr">
+      <c r="G61" s="30" t="inlineStr">
         <is>
           <t>MOBIL SHC AWARE GREASE EP 2</t>
         </is>
@@ -4712,7 +4778,7 @@
         </is>
       </c>
       <c r="J61" s="12" t="inlineStr"/>
-      <c r="K61" s="24" t="inlineStr">
+      <c r="K61" s="31" t="inlineStr">
         <is>
           <t>COMMENTS Note 3
 ★ 차트 표에는 'Maker supply' 로만 기재. SHC AWARE 는 ExxonMobil 의 EAL 제품군</t>
@@ -4734,7 +4800,7 @@
           <t>Crankcase (Synthetic)</t>
         </is>
       </c>
-      <c r="G62" s="29" t="inlineStr">
+      <c r="G62" s="30" t="inlineStr">
         <is>
           <t>MOBIL ARCTIC EAL 32</t>
         </is>
@@ -4750,7 +4816,7 @@
         </is>
       </c>
       <c r="J62" s="12" t="inlineStr"/>
-      <c r="K62" s="24" t="inlineStr">
+      <c r="K62" s="31" t="inlineStr">
         <is>
           <t>COMMENTS Note 1
 ★ 냉동기 압축기용 POE 오일. 제품명의 EAL 은 상표이며 VGP 환경친화 윤활유 아님</t>
@@ -4772,7 +4838,7 @@
           <t>Crankcase (Synthetic)</t>
         </is>
       </c>
-      <c r="G63" s="29" t="inlineStr">
+      <c r="G63" s="30" t="inlineStr">
         <is>
           <t>MOBIL ARCTIC EAL 32</t>
         </is>
@@ -4788,7 +4854,7 @@
         </is>
       </c>
       <c r="J63" s="12" t="inlineStr"/>
-      <c r="K63" s="24" t="inlineStr">
+      <c r="K63" s="31" t="inlineStr">
         <is>
           <t>COMMENTS Note 1
 ★ 상동</t>
@@ -4810,7 +4876,7 @@
           <t>Crankcase (Synthetic)</t>
         </is>
       </c>
-      <c r="G64" s="29" t="inlineStr">
+      <c r="G64" s="30" t="inlineStr">
         <is>
           <t>MOBIL ARCTIC EAL 32</t>
         </is>
@@ -4826,7 +4892,7 @@
         </is>
       </c>
       <c r="J64" s="12" t="inlineStr"/>
-      <c r="K64" s="24" t="inlineStr">
+      <c r="K64" s="31" t="inlineStr">
         <is>
           <t>COMMENTS Note 1
 ★ 상동</t>
@@ -4899,78 +4965,78 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>Klüber EAL 승인 현황 · SKF Marine EAL 리스트 (원문 발췌)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>[1] Klüber EAL 승인 현황 — 6척 장비 · 씰 메이커 관련 발췌</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>장비 · 씰 메이커</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
+      <c r="C4" s="33" t="inlineStr">
         <is>
           <t>Klüber 제품</t>
         </is>
       </c>
-      <c r="D4" s="31" t="inlineStr">
+      <c r="D4" s="33" t="inlineStr">
         <is>
           <t>승인 내용</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="E4" s="33" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="F4" s="31" t="inlineStr">
+      <c r="F4" s="33" t="inlineStr">
         <is>
           <t>6척 해당</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>3K / Korea</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>Rudder shaft &amp; pump</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>Klüberbio LG 39-701 N</t>
         </is>
       </c>
-      <c r="D5" s="32" t="inlineStr">
+      <c r="D5" s="34" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="E5" s="33" t="inlineStr">
+      <c r="E5" s="35" t="inlineStr">
         <is>
           <t>승인현황 p.6</t>
         </is>
       </c>
-      <c r="F5" s="34" t="inlineStr">
+      <c r="F5" s="36" t="inlineStr">
         <is>
           <t>●</t>
         </is>
@@ -5005,32 +5071,32 @@
       <c r="F6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>Kawasaki Heavy Industries / Japan</t>
         </is>
       </c>
-      <c r="B7" s="32" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>Thruster 기어유</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>Klüberbio EG 2-100</t>
         </is>
       </c>
-      <c r="D7" s="32" t="inlineStr">
+      <c r="D7" s="34" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="E7" s="33" t="inlineStr">
+      <c r="E7" s="35" t="inlineStr">
         <is>
           <t>승인현황 p.3 · 2018-08 업데이트 p.6</t>
         </is>
       </c>
-      <c r="F7" s="34" t="inlineStr">
+      <c r="F7" s="36" t="inlineStr">
         <is>
           <t>●</t>
         </is>
@@ -5065,32 +5131,32 @@
       <c r="F8" s="6" t="inlineStr"/>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Hyundai Heavy Industries / Korea</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>Thruster 기어유</t>
         </is>
       </c>
-      <c r="C9" s="32" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>Klüberbio EG 2-100</t>
         </is>
       </c>
-      <c r="D9" s="32" t="inlineStr">
+      <c r="D9" s="34" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="E9" s="33" t="inlineStr">
+      <c r="E9" s="35" t="inlineStr">
         <is>
           <t>승인현황 p.3 · 2018-08 업데이트 p.6</t>
         </is>
       </c>
-      <c r="F9" s="34" t="inlineStr">
+      <c r="F9" s="36" t="inlineStr">
         <is>
           <t>●</t>
         </is>
@@ -5153,354 +5219,354 @@
       <c r="F11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>WÄRTSILÄ Japan (former JMT)</t>
         </is>
       </c>
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>Stern tube 씰</t>
         </is>
       </c>
-      <c r="C12" s="32" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>Klüberbio RM 2-100 / RM 2-150</t>
         </is>
       </c>
-      <c r="D12" s="32" t="inlineStr">
+      <c r="D12" s="34" t="inlineStr">
         <is>
           <t>BIO FKM seal rings 승인</t>
         </is>
       </c>
-      <c r="E12" s="33" t="inlineStr">
+      <c r="E12" s="35" t="inlineStr">
         <is>
           <t>승인현황 p.1</t>
         </is>
       </c>
-      <c r="F12" s="34" t="inlineStr">
+      <c r="F12" s="36" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="32" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>WÄRTSILÄ Sweden AB (Cedervall)</t>
         </is>
       </c>
-      <c r="B13" s="32" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>Stern tube 씰</t>
         </is>
       </c>
-      <c r="C13" s="32" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>Klüberbio RM 2-100 / RM 2-150</t>
         </is>
       </c>
-      <c r="D13" s="32" t="inlineStr">
+      <c r="D13" s="34" t="inlineStr">
         <is>
           <t>RM 2-150 승인 · RM 2-100 은 신형 face seal 용</t>
         </is>
       </c>
-      <c r="E13" s="33" t="inlineStr">
+      <c r="E13" s="35" t="inlineStr">
         <is>
           <t>승인현황 p.1</t>
         </is>
       </c>
-      <c r="F13" s="34" t="inlineStr">
+      <c r="F13" s="36" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="32" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>WÄRTSILÄ UK (Deep Sea Seals)</t>
         </is>
       </c>
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>Stern tube 씰</t>
         </is>
       </c>
-      <c r="C14" s="32" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>Klüberbio RM 2-100 / RM 2-150</t>
         </is>
       </c>
-      <c r="D14" s="32" t="inlineStr">
+      <c r="D14" s="34" t="inlineStr">
         <is>
           <t>여러 씰 타입 승인 (최신 목록 별도 확인)</t>
         </is>
       </c>
-      <c r="E14" s="33" t="inlineStr">
+      <c r="E14" s="35" t="inlineStr">
         <is>
           <t>승인현황 p.1</t>
         </is>
       </c>
-      <c r="F14" s="34" t="inlineStr">
+      <c r="F14" s="36" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>WÄRTSILÄ Japan</t>
         </is>
       </c>
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>Rudder shaft 씰</t>
         </is>
       </c>
-      <c r="C15" s="32" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>Klüberbio AG 39-602</t>
         </is>
       </c>
-      <c r="D15" s="32" t="inlineStr">
+      <c r="D15" s="34" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="E15" s="33" t="inlineStr">
+      <c r="E15" s="35" t="inlineStr">
         <is>
           <t>승인현황 p.6</t>
         </is>
       </c>
-      <c r="F15" s="34" t="inlineStr">
+      <c r="F15" s="36" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>WÄRTSILÄ Propulsion / Holland</t>
         </is>
       </c>
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B16" s="34" t="inlineStr">
         <is>
           <t>Thruster 기어유</t>
         </is>
       </c>
-      <c r="C16" s="32" t="inlineStr">
+      <c r="C16" s="34" t="inlineStr">
         <is>
           <t>Klüberbio EG 2-150</t>
         </is>
       </c>
-      <c r="D16" s="32" t="inlineStr">
+      <c r="D16" s="34" t="inlineStr">
         <is>
           <t>승인 (사전 협의 필요)</t>
         </is>
       </c>
-      <c r="E16" s="33" t="inlineStr">
+      <c r="E16" s="35" t="inlineStr">
         <is>
           <t>승인현황 p.4 · 업데이트 p.9</t>
         </is>
       </c>
-      <c r="F16" s="34" t="inlineStr">
+      <c r="F16" s="36" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="32" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>KEMEL / Japan</t>
         </is>
       </c>
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>Stern tube 씰</t>
         </is>
       </c>
-      <c r="C17" s="32" t="inlineStr">
+      <c r="C17" s="34" t="inlineStr">
         <is>
           <t>Klüberbio RM 2-100 / RM 2-150</t>
         </is>
       </c>
-      <c r="D17" s="32" t="inlineStr">
+      <c r="D17" s="34" t="inlineStr">
         <is>
           <t>승인 — 단, 선박별 개별 승인 필요</t>
         </is>
       </c>
-      <c r="E17" s="33" t="inlineStr">
+      <c r="E17" s="35" t="inlineStr">
         <is>
           <t>승인현황 p.1</t>
         </is>
       </c>
-      <c r="F17" s="34" t="inlineStr">
+      <c r="F17" s="36" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="32" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>KEMEL / Japan</t>
         </is>
       </c>
-      <c r="B18" s="32" t="inlineStr">
+      <c r="B18" s="34" t="inlineStr">
         <is>
           <t>Thruster 씰</t>
         </is>
       </c>
-      <c r="C18" s="32" t="inlineStr">
+      <c r="C18" s="34" t="inlineStr">
         <is>
           <t>Klüberbio EG 2-100 / EG 2-150</t>
         </is>
       </c>
-      <c r="D18" s="32" t="inlineStr">
+      <c r="D18" s="34" t="inlineStr">
         <is>
           <t>신형 BIO seal ring 승인</t>
         </is>
       </c>
-      <c r="E18" s="33" t="inlineStr">
+      <c r="E18" s="35" t="inlineStr">
         <is>
           <t>승인현황 p.2</t>
         </is>
       </c>
-      <c r="F18" s="34" t="inlineStr">
+      <c r="F18" s="36" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="32" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>SKF Marine (Simplex, 구 Blohm+Voss)</t>
         </is>
       </c>
-      <c r="B19" s="32" t="inlineStr">
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>Stern tube 씰</t>
         </is>
       </c>
-      <c r="C19" s="32" t="inlineStr">
+      <c r="C19" s="34" t="inlineStr">
         <is>
           <t>Klüberbio RM 2-100 / RM 2-150</t>
         </is>
       </c>
-      <c r="D19" s="32" t="inlineStr">
+      <c r="D19" s="34" t="inlineStr">
         <is>
           <t>FKM (Viton Pod · Viton Bio) 씰링 재질 승인</t>
         </is>
       </c>
-      <c r="E19" s="33" t="inlineStr">
+      <c r="E19" s="35" t="inlineStr">
         <is>
           <t>승인현황 p.1</t>
         </is>
       </c>
-      <c r="F19" s="34" t="inlineStr">
+      <c r="F19" s="36" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="32" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>SKF Marine (Simplex)</t>
         </is>
       </c>
-      <c r="B20" s="32" t="inlineStr">
+      <c r="B20" s="34" t="inlineStr">
         <is>
           <t>Thruster 씰</t>
         </is>
       </c>
-      <c r="C20" s="32" t="inlineStr">
+      <c r="C20" s="34" t="inlineStr">
         <is>
           <t>Klüberbio EG 2-68 / 100 / 150</t>
         </is>
       </c>
-      <c r="D20" s="32" t="inlineStr">
+      <c r="D20" s="34" t="inlineStr">
         <is>
           <t>FKM (Viton Pod · Viton BIO) 승인</t>
         </is>
       </c>
-      <c r="E20" s="33" t="inlineStr">
+      <c r="E20" s="35" t="inlineStr">
         <is>
           <t>승인현황 p.2 · 업데이트 p.12~14</t>
         </is>
       </c>
-      <c r="F20" s="34" t="inlineStr">
+      <c r="F20" s="36" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="32" t="inlineStr">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>MAN Diesel &amp; Turbo SE / Denmark</t>
         </is>
       </c>
-      <c r="B21" s="32" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>Propeller cap</t>
         </is>
       </c>
-      <c r="C21" s="32" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
         <is>
           <t>Klüberbio BM 32-142 / AG 39-602 /
 LG 39-701 N</t>
         </is>
       </c>
-      <c r="D21" s="32" t="inlineStr">
+      <c r="D21" s="34" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="E21" s="33" t="inlineStr">
+      <c r="E21" s="35" t="inlineStr">
         <is>
           <t>승인현황 p.6</t>
         </is>
       </c>
-      <c r="F21" s="34" t="inlineStr">
+      <c r="F21" s="36" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="32" t="inlineStr">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>Mecklenburger Metallguss / Germany</t>
         </is>
       </c>
-      <c r="B22" s="32" t="inlineStr">
+      <c r="B22" s="34" t="inlineStr">
         <is>
           <t>Propeller cap</t>
         </is>
       </c>
-      <c r="C22" s="32" t="inlineStr">
+      <c r="C22" s="34" t="inlineStr">
         <is>
           <t>Klüberbio BM 32-142 / AG 39-602 /
 LG 39-701 N</t>
         </is>
       </c>
-      <c r="D22" s="32" t="inlineStr">
+      <c r="D22" s="34" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="E22" s="33" t="inlineStr">
+      <c r="E22" s="35" t="inlineStr">
         <is>
           <t>승인현황 p.6</t>
         </is>
       </c>
-      <c r="F22" s="34" t="inlineStr">
+      <c r="F22" s="36" t="inlineStr">
         <is>
           <t>●</t>
         </is>
@@ -5591,103 +5657,103 @@
       <c r="F25" s="6" t="inlineStr"/>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="30" t="inlineStr">
+      <c r="A28" s="32" t="inlineStr">
         <is>
           <t>[2] SKF Marine EAL 리스트 — 6척 관련 브랜드 및 Klüber 대응 후보 발췌</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="31" t="inlineStr">
+      <c r="A29" s="33" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="B29" s="31" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>제품명</t>
         </is>
       </c>
-      <c r="C29" s="31" t="inlineStr">
+      <c r="C29" s="33" t="inlineStr">
         <is>
           <t>점도 (cSt @40℃)</t>
         </is>
       </c>
-      <c r="D29" s="31" t="inlineStr">
+      <c r="D29" s="33" t="inlineStr">
         <is>
           <t>분류</t>
         </is>
       </c>
-      <c r="E29" s="31" t="inlineStr">
+      <c r="E29" s="33" t="inlineStr">
         <is>
           <t>씰링 재질</t>
         </is>
       </c>
-      <c r="F29" s="31" t="inlineStr">
+      <c r="F29" s="33" t="inlineStr">
         <is>
           <t>6척 사용 여부</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="33" t="inlineStr">
+      <c r="A30" s="35" t="inlineStr">
         <is>
           <t>Total Lubmarine</t>
         </is>
       </c>
-      <c r="B30" s="32" t="inlineStr">
+      <c r="B30" s="34" t="inlineStr">
         <is>
           <t>Bioneptan 150</t>
         </is>
       </c>
-      <c r="C30" s="33" t="inlineStr">
+      <c r="C30" s="35" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D30" s="33" t="inlineStr">
+      <c r="D30" s="35" t="inlineStr">
         <is>
           <t>Sterntube Oil</t>
         </is>
       </c>
-      <c r="E30" s="33" t="inlineStr">
+      <c r="E30" s="35" t="inlineStr">
         <is>
           <t>FKM Pod, FKM Bio</t>
         </is>
       </c>
-      <c r="F30" s="35" t="inlineStr">
+      <c r="F30" s="37" t="inlineStr">
         <is>
           <t>SK AUDACE 사용 중</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="33" t="inlineStr">
+      <c r="A31" s="35" t="inlineStr">
         <is>
           <t>Total Lubmarine</t>
         </is>
       </c>
-      <c r="B31" s="32" t="inlineStr">
+      <c r="B31" s="34" t="inlineStr">
         <is>
           <t>Bioneptan HT 100</t>
         </is>
       </c>
-      <c r="C31" s="33" t="inlineStr">
+      <c r="C31" s="35" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D31" s="33" t="inlineStr">
+      <c r="D31" s="35" t="inlineStr">
         <is>
           <t>Multipurpose Oil</t>
         </is>
       </c>
-      <c r="E31" s="33" t="inlineStr">
+      <c r="E31" s="35" t="inlineStr">
         <is>
           <t>FKM Pod, FKM Bio</t>
         </is>
       </c>
-      <c r="F31" s="35" t="inlineStr">
+      <c r="F31" s="37" t="inlineStr">
         <is>
           <t>PRISM AGILITY · SK AUDACE 사용 중</t>
         </is>
@@ -5790,32 +5856,32 @@
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="33" t="inlineStr">
+      <c r="A35" s="35" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="B35" s="32" t="inlineStr">
+      <c r="B35" s="34" t="inlineStr">
         <is>
           <t>Mobil SHC Aware Gear 100</t>
         </is>
       </c>
-      <c r="C35" s="33" t="inlineStr">
+      <c r="C35" s="35" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D35" s="33" t="inlineStr">
+      <c r="D35" s="35" t="inlineStr">
         <is>
           <t>Gear Oil</t>
         </is>
       </c>
-      <c r="E35" s="33" t="inlineStr">
+      <c r="E35" s="35" t="inlineStr">
         <is>
           <t>FKM Pod, FKM Bio</t>
         </is>
       </c>
-      <c r="F35" s="35" t="inlineStr">
+      <c r="F35" s="37" t="inlineStr">
         <is>
           <t>PRISM AGILITY 사용 중</t>
         </is>
@@ -6071,7 +6137,7 @@
           <t>FKM Pod, FKM Bio</t>
         </is>
       </c>
-      <c r="F43" s="36" t="inlineStr">
+      <c r="F43" s="38" t="inlineStr">
         <is>
           <t>대응 후보</t>
         </is>
@@ -6103,7 +6169,7 @@
           <t>FKM Pod, FKM Bio</t>
         </is>
       </c>
-      <c r="F44" s="36" t="inlineStr">
+      <c r="F44" s="38" t="inlineStr">
         <is>
           <t>대응 후보</t>
         </is>
@@ -6167,7 +6233,7 @@
           <t>FKM Pod, FKM Bio</t>
         </is>
       </c>
-      <c r="F46" s="36" t="inlineStr">
+      <c r="F46" s="38" t="inlineStr">
         <is>
           <t>대응 후보</t>
         </is>

--- a/EAL_제품_메이커_정리_6척.xlsx
+++ b/EAL_제품_메이커_정리_6척.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -111,7 +111,7 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="00808080"/>
+      <color rgb="001F3864"/>
       <sz val="9"/>
     </font>
     <font>
@@ -126,14 +126,8 @@
       <color rgb="001F7A3D"/>
       <sz val="12"/>
     </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -178,6 +172,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF0F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -240,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -291,6 +290,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -349,7 +351,7 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1477,15 +1479,16 @@
           <t>ORIENTAL · TANKTECH 등</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Klüber 자료 범위 밖</t>
+      <c r="F19" s="19" t="inlineStr">
+        <is>
+          <t>Klüberbio AM 92-142
+(210068 25 KG / 210021 180 KG)</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>— (Klüber 자료는 선미관 · 스러스터 ·
-씰/베어링 그리스 한정)</t>
+          <t>씰 메이커 승인 불요 용도
+(선미관 · 스러스터 씰과 달리 승인 전제 없음)</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -1493,9 +1496,9 @@
           <t>대상 아님 (그리스)</t>
         </is>
       </c>
-      <c r="I19" s="19" t="inlineStr">
-        <is>
-          <t>해당 없음</t>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>대응 확정</t>
         </is>
       </c>
     </row>
@@ -1523,14 +1526,15 @@
 Sangsangin · OPCO</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Klüber 자료 범위 밖</t>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>Klüberbio AM 92-142
+(210068 25 KG / 210021 180 KG)</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>씰 메이커 승인 불요 용도</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -1538,9 +1542,9 @@
           <t>대상 아님 (그리스)</t>
         </is>
       </c>
-      <c r="I20" s="19" t="inlineStr">
-        <is>
-          <t>해당 없음</t>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>대응 확정</t>
         </is>
       </c>
     </row>
@@ -1567,14 +1571,15 @@
 SHIN MYUNG · KTMI · ORIENTAL</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Klüber 자료 범위 밖</t>
+      <c r="F21" s="19" t="inlineStr">
+        <is>
+          <t>Klüberbio AM 92-142
+(210068 25 KG / 210021 180 KG)</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>씰 메이커 승인 불요 용도</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -1582,9 +1587,9 @@
           <t>대상 아님 (그리스)</t>
         </is>
       </c>
-      <c r="I21" s="19" t="inlineStr">
-        <is>
-          <t>해당 없음</t>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>대응 확정</t>
         </is>
       </c>
     </row>
@@ -1614,14 +1619,15 @@
           <t>(전선 공통)</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>Klüber 자료 범위 밖</t>
+      <c r="F22" s="19" t="inlineStr">
+        <is>
+          <t>Klüberbio GE 32-681
+(210098 25 KG / 210094 180 KG)</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>씰 메이커 승인 불요 용도</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -1629,9 +1635,9 @@
           <t>대상 아님 (그리스)</t>
         </is>
       </c>
-      <c r="I22" s="19" t="inlineStr">
-        <is>
-          <t>해당 없음</t>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>대응 확정</t>
         </is>
       </c>
     </row>
@@ -1663,14 +1669,15 @@
           <t>Winch · Crane · Davit 등</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Klüberbio AG 39-602 계열</t>
+      <c r="F23" s="19" t="inlineStr">
+        <is>
+          <t>Klüberbio AG 39-602 N
+(210077 25 KG / 210078 180 KG)</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>씰 메이커 승인 불요 용도</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
@@ -1678,9 +1685,9 @@
           <t>대상 아님 (그리스)</t>
         </is>
       </c>
-      <c r="I23" s="19" t="inlineStr">
-        <is>
-          <t>해당 없음</t>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>대응 확정</t>
         </is>
       </c>
     </row>
@@ -1734,12 +1741,12 @@
       </c>
     </row>
     <row r="26" ht="168" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>▣ 읽는 법
   · 승인 확인 = 현재 쓰는 제품과 같은 용도로 해당 장비 메이커가 Klüber EAL 을 승인한 이력이 있음 → 대체 검토 가능
   · 확인 필요 = 장비 메이커가 Klüber 승인 목록에 없음 → Klüber 로 바꾸려면 해당 메이커 승인을 별도로 받아야 함
-  · 해당 없음 = 와이어로프 · 개방기어용 그리스로, Klüber 자료(선미관 · 스러스터 · 씰/베어링) 범위 밖
+  · 대응 확정 = 와이어로프 · 개방기어 등 씰 메이커 승인이 전제되지 않는 용도로, 대응 품목만 확정한 것
   · SKF Marine EAL 리스트는 Simplex 선미관 씰용 「오일」 전용 목록입니다. 그리스가 미등재인 것은 결격이 아니라 대상이 아닌 것입니다.
 ▣ 눈에 띄는 두 가지
   · Rudder Carrier — 3K INDUSTRY 장비를 쓰는 3척(PUTERI SABAH · MARVEL DOVE · PRISM AGILITY)은 Klüber 가 3K 로부터 rudder shaft &amp; pump 승인을 이미 받아둔 상태입니다. 3척이 지금 서로 다른 제품(Margrease · Clarity Syn EA 0 · Tectyl ECO)을 쓰고 있어 Klüberbio LG 39-701 N 하나로 통일할 여지가 있습니다.
@@ -1834,26 +1841,26 @@
       </c>
     </row>
     <row r="5" ht="92" customHeight="1">
-      <c r="A5" s="21" t="n">
+      <c r="A5" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>TotalEnergies
 Lubmarine</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>생분해성 다목적 EP 그리스</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t>AL SAKHAMAH
 BU FINTAS
@@ -1861,7 +1868,7 @@
 SK AUDACE</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="F5" s="24" t="inlineStr">
         <is>
           <t>Propeller Cap · Rudder Carrier ·
 Steering Gear Grease Pump ·
@@ -1870,7 +1877,7 @@
 Emergency Towing · General Greasing</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>● Propeller Cap 용
    210016  KLÜBERBIO BM 32-142 25 KG
@@ -1920,49 +1927,47 @@
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>직접 대응 품목 미확인
-후보 (용도 확인 필요)
-   210068  KLÜBERBIO AM 92-142 25 KG
-   210021  KLÜBERBIO AM 92-142 180 KG</t>
+          <t>210068  KLÜBERBIO AM 92-142 25 KG
+210021  KLÜBERBIO AM 92-142 180 KG
+→ 와이어로프용 점착 그리스</t>
         </is>
       </c>
     </row>
     <row r="7" ht="92" customHeight="1">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>BIO OG+</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>TotalEnergies
 Lubmarine</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>생분해성 개방기어용 그리스</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t>BU FINTAS</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr">
+      <c r="F7" s="24" t="inlineStr">
         <is>
           <t>General Greasing — Open Gears</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>직접 대응 품목 미확인
-후보 (용도 확인 필요)
-   210098  KLÜBERBIO GE 32-681 25 KG
-   210094  KLÜBERBIO GE 32-681 180 KG
+          <t>210098  KLÜBERBIO GE 32-681 25 KG
+210094  KLÜBERBIO GE 32-681 180 KG
+→ 개방기어용 그리스
 ※ 210060 GRAFLOSCON C-SG 0 ULTRA 는
    개방기어용이나 BIO 계열 아님</t>
         </is>
@@ -1999,7 +2004,7 @@
           <t>Bow Thruster — Enclosed Gears</t>
         </is>
       </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>210004  KLÜBERBIO EG 2-100 200 LTR
 → 동일 점도(VG 100) 스러스터 기어유
@@ -2008,36 +2013,36 @@
       </c>
     </row>
     <row r="9" ht="92" customHeight="1">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>BIONEPTAN 150</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>TotalEnergies
 Lubmarine</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t>생분해성 선미관유 (ISO VG 150)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>SK AUDACE</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="24" t="inlineStr">
         <is>
           <t>Stern Tube — Bearings &amp; Seals</t>
         </is>
       </c>
-      <c r="G9" s="24" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t>210056  KLÜBERBIO RM 2-150 200 LTR
 → 동일 점도(VG 150) 선미관유
@@ -2081,45 +2086,44 @@
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>직접 대응 품목 미확인
-후보 (용도 확인 필요)
-   210068  KLÜBERBIO AM 92-142 25 KG
-   210021  KLÜBERBIO AM 92-142 180 KG</t>
+          <t>210068  KLÜBERBIO AM 92-142 25 KG
+210021  KLÜBERBIO AM 92-142 180 KG
+→ 와이어로프용 점착 그리스</t>
         </is>
       </c>
     </row>
     <row r="11" ht="92" customHeight="1">
-      <c r="A11" s="21" t="n">
+      <c r="A11" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Shell Naturelle S5 Grease
 V120P 2</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>Shell</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>생분해성 다목적 그리스 (NLGI 2)</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>PUTERI SABAH</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="24" t="inlineStr">
         <is>
           <t>Propeller Bonnet / Cap Grease Filling ·
 General Grease Points</t>
         </is>
       </c>
-      <c r="G11" s="24" t="inlineStr">
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>210016  KLÜBERBIO BM 32-142 25 KG
 → Propeller Cap 용 (MAN D&amp;T · MMG 승인)
@@ -2165,43 +2169,43 @@
         <is>
           <t>● Propeller Bonnet 용
    210016  KLÜBERBIO BM 32-142 25 KG
-● Wire Ropes · Open Gears 용
-   직접 대응 품목 미확인
-   후보 210068 / 210021 AM 92-142
-        210098 / 210094 GE 32-681</t>
+● Wire Ropes 용
+   210068 / 210021  KLÜBERBIO AM 92-142
+● Open Gears 용
+   210098 / 210094  KLÜBERBIO GE 32-681</t>
         </is>
       </c>
     </row>
     <row r="13" ht="92" customHeight="1">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE 0</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>Chevron</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="24" t="inlineStr">
         <is>
           <t>합성 생분해성 그리스 (0번 주도)</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="24" t="inlineStr">
         <is>
           <t>MARVEL DOVE</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F13" s="24" t="inlineStr">
         <is>
           <t>Rudder Carrier — Grease Points</t>
         </is>
       </c>
-      <c r="G13" s="24" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t>210028  KLÜBERBIO LG 39-701 N 18 KG
 210072  KLÜBERBIO LG 39-701 N 180 KG
@@ -2239,7 +2243,7 @@
           <t>Bow Thruster 초기 충전유</t>
         </is>
       </c>
-      <c r="G14" s="24" t="inlineStr">
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>210004  KLÜBERBIO EG 2-100 200 LTR
 → 동일 점도(VG 100) 스러스터 기어유
@@ -2248,35 +2252,35 @@
       </c>
     </row>
     <row r="15" ht="92" customHeight="1">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>MOBIL SHC AWARE GREASE EP 2</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="24" t="inlineStr">
         <is>
           <t>합성 생분해성 EP 그리스</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t>SK AUDACE</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
+      <c r="F15" s="24" t="inlineStr">
         <is>
           <t>Rudder Carrier — Grease Pump</t>
         </is>
       </c>
-      <c r="G15" s="25" t="inlineStr">
+      <c r="G15" s="26" t="inlineStr">
         <is>
           <t>210028  KLÜBERBIO LG 39-701 N 18 KG
 210072  KLÜBERBIO LG 39-701 N 180 KG
@@ -2314,7 +2318,7 @@
           <t>Rudder Carrier — Grease Points</t>
         </is>
       </c>
-      <c r="G16" s="24" t="inlineStr">
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t>210028  KLÜBERBIO LG 39-701 N 18 KG
 210072  KLÜBERBIO LG 39-701 N 180 KG
@@ -2331,7 +2335,7 @@
           <t>Margrease EP 0</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
         <is>
           <t>확인 필요</t>
         </is>
@@ -2351,7 +2355,7 @@
           <t>Rudder Carrier — Grease Filling</t>
         </is>
       </c>
-      <c r="G17" s="24" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>210028  KLÜBERBIO LG 39-701 N 18 KG
 210072  KLÜBERBIO LG 39-701 N 180 KG
@@ -2393,7 +2397,7 @@
 BU FINTAS 초기 충전유</t>
         </is>
       </c>
-      <c r="G18" s="25" t="inlineStr">
+      <c r="G18" s="26" t="inlineStr">
         <is>
           <t>210170  KLÜBER SUMMIT RPE 32 (PAIL 20 LTR)
 210175  KLÜBER SUMMIT RPE 32 (DRUM 200 LTR)
@@ -2403,15 +2407,15 @@
       </c>
     </row>
     <row r="20" ht="118" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>▣ Klüber 대응 품목 읽는 법
   · 초록색 = 용도 · 점도 · 장비 메이커 승인까지 맞아떨어지는 대응 품목
   · 노란색 = 대응 품목은 있으나 별도 확인이 필요 (용도 미확인 / 장비 메이커 승인 이력 없음 / 주도 등급 상이)
   · 품목번호는 Wilhelmsen 공급 Klüber 품목 리스트 기준이며, 포장 단위(25 KG · 180 KG · 200 LTR 등)까지 표기했습니다.
   · 그리스는 하나의 현재 제품이 여러 부위에 쓰이는 경우가 많아, Klüber 쪽은 부위별로 품목이 갈립니다. 「● 부위 → 품목」 형태로 나눠 적었습니다.
-▣ 대응 품목이 확정되지 않은 두 용도
-  · 와이어로프 점착 그리스 (BIOADHESIVE PLUS · Naturelle S2 Grease · Clarity Syn EA Grease) 와 개방기어 그리스 (BIO OG+) 는 Klüber 승인 자료 · SKF 리스트 어느 쪽에도 해당 용도가 없습니다. 품목 리스트상 KLÜBERBIO AM 92-142 와 GE 32-681 이 후보이나, 두 품목의 용도는 제공된 자료로 확인되지 않아 Klüber 확인이 필요합니다.
+▣ 남은 확인 항목
+  · 와이어로프용 AM 92-142 · 개방기어용 GE 32-681 은 고객 확인으로 확정했습니다. 두 품목은 Klüber 승인 자료 · SKF 리스트에 해당 용도 기재가 없으나, 이들 부위는 선미관 · 스러스터 씰과 달리 씰 메이커 승인이 전제되지 않는 용도입니다.
   · MOBIL Arctic EAL 32 는 냉동기 압축기유로 EAL 이 아닙니다. 대응품으로 적은 KLÜBER SUMMIT RPE 32 도 EAL 이 아니며, 점도(VG 32)만 같습니다. 냉매 적합성은 별도 확인이 필요합니다.
   · Klüber 승인 근거는 2018년 자료 기준입니다. 상세 근거는 'Klüber·SKF 참조' 시트를 보십시오.</t>
         </is>
@@ -2450,7 +2454,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>선박별 EAL 적용 상세 (Lubrication Chart 원문 기준)</t>
         </is>
@@ -2526,17 +2530,17 @@
           <t>PUTERI SABAH</t>
         </is>
       </c>
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>9975521</t>
         </is>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>Shell</t>
         </is>
       </c>
-      <c r="D5" s="28" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>v2 / 2025-01-15</t>
         </is>
@@ -2551,7 +2555,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G5" s="29" t="inlineStr">
+      <c r="G5" s="30" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -2588,7 +2592,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G6" s="29" t="inlineStr">
+      <c r="G6" s="30" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -2625,7 +2629,7 @@
           <t>Towing Wire</t>
         </is>
       </c>
-      <c r="G7" s="29" t="inlineStr">
+      <c r="G7" s="30" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -2662,7 +2666,7 @@
           <t>Open Gears &amp; Wire Ropes</t>
         </is>
       </c>
-      <c r="G8" s="29" t="inlineStr">
+      <c r="G8" s="30" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -2699,7 +2703,7 @@
           <t>Open Gears &amp; Wire Ropes</t>
         </is>
       </c>
-      <c r="G9" s="29" t="inlineStr">
+      <c r="G9" s="30" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -2736,7 +2740,7 @@
           <t>Open Gears &amp; Wire Ropes</t>
         </is>
       </c>
-      <c r="G10" s="29" t="inlineStr">
+      <c r="G10" s="30" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -2773,7 +2777,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G11" s="29" t="inlineStr">
+      <c r="G11" s="30" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -2814,7 +2818,7 @@
           <t>Open Gears &amp; Wire Ropes</t>
         </is>
       </c>
-      <c r="G12" s="29" t="inlineStr">
+      <c r="G12" s="30" t="inlineStr">
         <is>
           <t>Shell Naturelle S2 Grease A600P 1.5</t>
         </is>
@@ -2851,7 +2855,7 @@
           <t>Grease Filling</t>
         </is>
       </c>
-      <c r="G13" s="29" t="inlineStr">
+      <c r="G13" s="30" t="inlineStr">
         <is>
           <t>Shell Naturelle S5 Grease V120P 2</t>
         </is>
@@ -2888,7 +2892,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G14" s="29" t="inlineStr">
+      <c r="G14" s="30" t="inlineStr">
         <is>
           <t>Shell Naturelle S5 Grease V120P 2</t>
         </is>
@@ -2925,7 +2929,7 @@
           <t>Grease Filling</t>
         </is>
       </c>
-      <c r="G15" s="29" t="inlineStr">
+      <c r="G15" s="30" t="inlineStr">
         <is>
           <t>Margrease EP 0</t>
         </is>
@@ -2958,18 +2962,18 @@
           <t>AL SAKHAMAH</t>
         </is>
       </c>
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>9986051</t>
         </is>
       </c>
-      <c r="C16" s="28" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>TotalEnergies
 Lubmarine</t>
         </is>
       </c>
-      <c r="D16" s="28" t="inlineStr">
+      <c r="D16" s="29" t="inlineStr">
         <is>
           <t>R3 / 2025-04-16</t>
         </is>
@@ -2984,7 +2988,7 @@
           <t>Towing Pennant</t>
         </is>
       </c>
-      <c r="G16" s="29" t="inlineStr">
+      <c r="G16" s="30" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -3021,7 +3025,7 @@
           <t>Rudder Trunk</t>
         </is>
       </c>
-      <c r="G17" s="29" t="inlineStr">
+      <c r="G17" s="30" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -3059,7 +3063,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="G18" s="29" t="inlineStr">
+      <c r="G18" s="30" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -3087,18 +3091,18 @@
           <t>BU FINTAS</t>
         </is>
       </c>
-      <c r="B19" s="28" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>9976824</t>
         </is>
       </c>
-      <c r="C19" s="28" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>TotalEnergies
 Lubmarine</t>
         </is>
       </c>
-      <c r="D19" s="28" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>R2 / 2024-08-07</t>
         </is>
@@ -3113,7 +3117,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="G19" s="29" t="inlineStr">
+      <c r="G19" s="30" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -3150,7 +3154,7 @@
           <t>Grease Pump</t>
         </is>
       </c>
-      <c r="G20" s="29" t="inlineStr">
+      <c r="G20" s="30" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -3191,7 +3195,7 @@
           <t>Grease Filling</t>
         </is>
       </c>
-      <c r="G21" s="29" t="inlineStr">
+      <c r="G21" s="30" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -3228,7 +3232,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G22" s="29" t="inlineStr">
+      <c r="G22" s="30" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -3265,7 +3269,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G23" s="29" t="inlineStr">
+      <c r="G23" s="30" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -3302,7 +3306,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G24" s="29" t="inlineStr">
+      <c r="G24" s="30" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -3339,7 +3343,7 @@
           <t>Open Gears</t>
         </is>
       </c>
-      <c r="G25" s="29" t="inlineStr">
+      <c r="G25" s="30" t="inlineStr">
         <is>
           <t>BIO OG+</t>
         </is>
@@ -3376,7 +3380,7 @@
           <t>초기 충전유</t>
         </is>
       </c>
-      <c r="G26" s="30" t="inlineStr">
+      <c r="G26" s="31" t="inlineStr">
         <is>
           <t>MOBIL ARCTIC EAL 32</t>
         </is>
@@ -3392,7 +3396,7 @@
         </is>
       </c>
       <c r="J26" s="12" t="inlineStr"/>
-      <c r="K26" s="31" t="inlineStr">
+      <c r="K26" s="32" t="inlineStr">
         <is>
           <t>제품명에 EAL 포함
 ★ 냉동기 압축기용 POE 오일. 제품명의 EAL 은 상표이며 VGP 환경친화 윤활유 아님</t>
@@ -3405,17 +3409,17 @@
           <t>MARVEL DOVE</t>
         </is>
       </c>
-      <c r="B27" s="28" t="inlineStr">
+      <c r="B27" s="29" t="inlineStr">
         <is>
           <t>9964182</t>
         </is>
       </c>
-      <c r="C27" s="28" t="inlineStr">
+      <c r="C27" s="29" t="inlineStr">
         <is>
           <t>Chevron</t>
         </is>
       </c>
-      <c r="D27" s="28" t="inlineStr">
+      <c r="D27" s="29" t="inlineStr">
         <is>
           <t>2024-06-17</t>
         </is>
@@ -3430,7 +3434,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G27" s="29" t="inlineStr">
+      <c r="G27" s="30" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -3467,7 +3471,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G28" s="29" t="inlineStr">
+      <c r="G28" s="30" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -3508,7 +3512,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G29" s="29" t="inlineStr">
+      <c r="G29" s="30" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -3549,7 +3553,7 @@
           <t>Open Gears &amp; Wire Ropes</t>
         </is>
       </c>
-      <c r="G30" s="29" t="inlineStr">
+      <c r="G30" s="30" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -3586,7 +3590,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G31" s="29" t="inlineStr">
+      <c r="G31" s="30" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -3623,7 +3627,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G32" s="29" t="inlineStr">
+      <c r="G32" s="30" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -3660,7 +3664,7 @@
           <t>Towing Wire</t>
         </is>
       </c>
-      <c r="G33" s="29" t="inlineStr">
+      <c r="G33" s="30" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -3697,7 +3701,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G34" s="29" t="inlineStr">
+      <c r="G34" s="30" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -3739,7 +3743,7 @@
           <t>Brush Applied</t>
         </is>
       </c>
-      <c r="G35" s="29" t="inlineStr">
+      <c r="G35" s="30" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE</t>
         </is>
@@ -3776,7 +3780,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G36" s="29" t="inlineStr">
+      <c r="G36" s="30" t="inlineStr">
         <is>
           <t>CLARITY SYN EA GREASE 0</t>
         </is>
@@ -3813,7 +3817,7 @@
           <t>Crankcase</t>
         </is>
       </c>
-      <c r="G37" s="30" t="inlineStr">
+      <c r="G37" s="31" t="inlineStr">
         <is>
           <t>MOBIL Arctic EAL 32</t>
         </is>
@@ -3829,7 +3833,7 @@
         </is>
       </c>
       <c r="J37" s="12" t="inlineStr"/>
-      <c r="K37" s="31" t="inlineStr">
+      <c r="K37" s="32" t="inlineStr">
         <is>
           <t>제품명에 EAL 포함
 ★ 냉동기 압축기용 POE 오일 · Initial Fill &amp; Owner Supplied. VGP 환경친화 윤활유 아님</t>
@@ -3851,7 +3855,7 @@
           <t>Crankcase</t>
         </is>
       </c>
-      <c r="G38" s="30" t="inlineStr">
+      <c r="G38" s="31" t="inlineStr">
         <is>
           <t>MOBIL Arctic EAL 32</t>
         </is>
@@ -3867,7 +3871,7 @@
         </is>
       </c>
       <c r="J38" s="12" t="inlineStr"/>
-      <c r="K38" s="31" t="inlineStr">
+      <c r="K38" s="32" t="inlineStr">
         <is>
           <t>제품명에 EAL 포함
 ★ 상동 · Initial Fill &amp; Owner Supplied</t>
@@ -3889,7 +3893,7 @@
           <t>Crankcase</t>
         </is>
       </c>
-      <c r="G39" s="30" t="inlineStr">
+      <c r="G39" s="31" t="inlineStr">
         <is>
           <t>MOBIL Arctic EAL 32</t>
         </is>
@@ -3905,7 +3909,7 @@
         </is>
       </c>
       <c r="J39" s="12" t="inlineStr"/>
-      <c r="K39" s="31" t="inlineStr">
+      <c r="K39" s="32" t="inlineStr">
         <is>
           <t>제품명에 EAL 포함
 ★ 상동 · Initial Fill &amp; Owner Supplied</t>
@@ -3918,18 +3922,18 @@
           <t>PRISM AGILITY</t>
         </is>
       </c>
-      <c r="B40" s="28" t="inlineStr">
+      <c r="B40" s="29" t="inlineStr">
         <is>
           <t>9810549</t>
         </is>
       </c>
-      <c r="C40" s="28" t="inlineStr">
+      <c r="C40" s="29" t="inlineStr">
         <is>
           <t>TotalEnergies
 Lubmarine</t>
         </is>
       </c>
-      <c r="D40" s="28" t="inlineStr">
+      <c r="D40" s="29" t="inlineStr">
         <is>
           <t>R3 / 2024-01-11</t>
         </is>
@@ -3944,7 +3948,7 @@
           <t>Enclosed Gears</t>
         </is>
       </c>
-      <c r="G40" s="29" t="inlineStr">
+      <c r="G40" s="30" t="inlineStr">
         <is>
           <t>BIONEPTAN HT 100</t>
         </is>
@@ -3985,7 +3989,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G41" s="29" t="inlineStr">
+      <c r="G41" s="30" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -4026,7 +4030,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G42" s="29" t="inlineStr">
+      <c r="G42" s="30" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -4068,7 +4072,7 @@
           <t>초기 충전유 (First oil)</t>
         </is>
       </c>
-      <c r="G43" s="30" t="inlineStr">
+      <c r="G43" s="31" t="inlineStr">
         <is>
           <t>MOBIL SHC AWARE GEAR 100</t>
         </is>
@@ -4088,7 +4092,7 @@
           <t>KT-219B5</t>
         </is>
       </c>
-      <c r="K43" s="31" t="inlineStr">
+      <c r="K43" s="32" t="inlineStr">
         <is>
           <t>COMMENTS Note 1
 ★ 차트 표에는 (EAL) 미표기. SHC AWARE 는 ExxonMobil 의 EAL 기어유 제품군</t>
@@ -4110,7 +4114,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G44" s="30" t="inlineStr">
+      <c r="G44" s="31" t="inlineStr">
         <is>
           <t>HOUTON TECTYL G OS 5550 ECO</t>
         </is>
@@ -4130,7 +4134,7 @@
           <t>MSB-360-T6M</t>
         </is>
       </c>
-      <c r="K44" s="31" t="inlineStr">
+      <c r="K44" s="32" t="inlineStr">
         <is>
           <t>COMMENTS Note 3
 ★ 차트 표에는 'Maker supply' 로만 기재. 차트 원문 표기 'HOUTON' (Houghton 오기로 추정)</t>
@@ -4143,18 +4147,18 @@
           <t>SK AUDACE</t>
         </is>
       </c>
-      <c r="B45" s="28" t="inlineStr">
+      <c r="B45" s="29" t="inlineStr">
         <is>
           <t>9693161</t>
         </is>
       </c>
-      <c r="C45" s="28" t="inlineStr">
+      <c r="C45" s="29" t="inlineStr">
         <is>
           <t>TotalEnergies
 Lubmarine</t>
         </is>
       </c>
-      <c r="D45" s="28" t="inlineStr">
+      <c r="D45" s="29" t="inlineStr">
         <is>
           <t>R3 / 2024-01-11</t>
         </is>
@@ -4169,7 +4173,7 @@
           <t>Bearings &amp; Seals</t>
         </is>
       </c>
-      <c r="G45" s="30" t="inlineStr">
+      <c r="G45" s="31" t="inlineStr">
         <is>
           <t>BIONEPTAN 150</t>
         </is>
@@ -4185,7 +4189,7 @@
         </is>
       </c>
       <c r="J45" s="12" t="inlineStr"/>
-      <c r="K45" s="31" t="inlineStr">
+      <c r="K45" s="32" t="inlineStr">
         <is>
           <t>(EAL)
 ★ 본 6척 중 유일하게 Stern Tube 에 EAL 적용 (타 5척은 광유)</t>
@@ -4207,7 +4211,7 @@
           <t>Enclosed Gears</t>
         </is>
       </c>
-      <c r="G46" s="29" t="inlineStr">
+      <c r="G46" s="30" t="inlineStr">
         <is>
           <t>BIONEPTAN HT 100</t>
         </is>
@@ -4244,7 +4248,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G47" s="29" t="inlineStr">
+      <c r="G47" s="30" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -4281,7 +4285,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G48" s="29" t="inlineStr">
+      <c r="G48" s="30" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -4318,7 +4322,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G49" s="29" t="inlineStr">
+      <c r="G49" s="30" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -4355,7 +4359,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G50" s="29" t="inlineStr">
+      <c r="G50" s="30" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -4392,7 +4396,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G51" s="29" t="inlineStr">
+      <c r="G51" s="30" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -4429,7 +4433,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G52" s="29" t="inlineStr">
+      <c r="G52" s="30" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -4466,7 +4470,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G53" s="29" t="inlineStr">
+      <c r="G53" s="30" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -4503,7 +4507,7 @@
           <t>Grease Points</t>
         </is>
       </c>
-      <c r="G54" s="29" t="inlineStr">
+      <c r="G54" s="30" t="inlineStr">
         <is>
           <t>BIOMULTIS EP 2</t>
         </is>
@@ -4540,7 +4544,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G55" s="29" t="inlineStr">
+      <c r="G55" s="30" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -4577,7 +4581,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G56" s="29" t="inlineStr">
+      <c r="G56" s="30" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -4614,7 +4618,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G57" s="29" t="inlineStr">
+      <c r="G57" s="30" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -4651,7 +4655,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G58" s="29" t="inlineStr">
+      <c r="G58" s="30" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -4688,7 +4692,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G59" s="29" t="inlineStr">
+      <c r="G59" s="30" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -4725,7 +4729,7 @@
           <t>Wire Ropes</t>
         </is>
       </c>
-      <c r="G60" s="29" t="inlineStr">
+      <c r="G60" s="30" t="inlineStr">
         <is>
           <t>BIOADHESIVE PLUS</t>
         </is>
@@ -4762,7 +4766,7 @@
           <t>Grease Pump</t>
         </is>
       </c>
-      <c r="G61" s="30" t="inlineStr">
+      <c r="G61" s="31" t="inlineStr">
         <is>
           <t>MOBIL SHC AWARE GREASE EP 2</t>
         </is>
@@ -4778,7 +4782,7 @@
         </is>
       </c>
       <c r="J61" s="12" t="inlineStr"/>
-      <c r="K61" s="31" t="inlineStr">
+      <c r="K61" s="32" t="inlineStr">
         <is>
           <t>COMMENTS Note 3
 ★ 차트 표에는 'Maker supply' 로만 기재. SHC AWARE 는 ExxonMobil 의 EAL 제품군</t>
@@ -4800,7 +4804,7 @@
           <t>Crankcase (Synthetic)</t>
         </is>
       </c>
-      <c r="G62" s="30" t="inlineStr">
+      <c r="G62" s="31" t="inlineStr">
         <is>
           <t>MOBIL ARCTIC EAL 32</t>
         </is>
@@ -4816,7 +4820,7 @@
         </is>
       </c>
       <c r="J62" s="12" t="inlineStr"/>
-      <c r="K62" s="31" t="inlineStr">
+      <c r="K62" s="32" t="inlineStr">
         <is>
           <t>COMMENTS Note 1
 ★ 냉동기 압축기용 POE 오일. 제품명의 EAL 은 상표이며 VGP 환경친화 윤활유 아님</t>
@@ -4838,7 +4842,7 @@
           <t>Crankcase (Synthetic)</t>
         </is>
       </c>
-      <c r="G63" s="30" t="inlineStr">
+      <c r="G63" s="31" t="inlineStr">
         <is>
           <t>MOBIL ARCTIC EAL 32</t>
         </is>
@@ -4854,7 +4858,7 @@
         </is>
       </c>
       <c r="J63" s="12" t="inlineStr"/>
-      <c r="K63" s="31" t="inlineStr">
+      <c r="K63" s="32" t="inlineStr">
         <is>
           <t>COMMENTS Note 1
 ★ 상동</t>
@@ -4876,7 +4880,7 @@
           <t>Crankcase (Synthetic)</t>
         </is>
       </c>
-      <c r="G64" s="30" t="inlineStr">
+      <c r="G64" s="31" t="inlineStr">
         <is>
           <t>MOBIL ARCTIC EAL 32</t>
         </is>
@@ -4892,7 +4896,7 @@
         </is>
       </c>
       <c r="J64" s="12" t="inlineStr"/>
-      <c r="K64" s="31" t="inlineStr">
+      <c r="K64" s="32" t="inlineStr">
         <is>
           <t>COMMENTS Note 1
 ★ 상동</t>
@@ -4900,7 +4904,7 @@
       </c>
     </row>
     <row r="66" ht="100" customHeight="1">
-      <c r="A66" s="20" t="inlineStr">
+      <c r="A66" s="21" t="inlineStr">
         <is>
           <t>▣ 출처
   · PUTERI SABAH — Shell Lubrication Survey, Version 2, 2025-01-15 (Vessel Code 806179)
@@ -4965,78 +4969,78 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>Klüber EAL 승인 현황 · SKF Marine EAL 리스트 (원문 발췌)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>[1] Klüber EAL 승인 현황 — 6척 장비 · 씰 메이커 관련 발췌</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>장비 · 씰 메이커</t>
         </is>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="C4" s="33" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>Klüber 제품</t>
         </is>
       </c>
-      <c r="D4" s="33" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>승인 내용</t>
         </is>
       </c>
-      <c r="E4" s="33" t="inlineStr">
+      <c r="E4" s="34" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="F4" s="33" t="inlineStr">
+      <c r="F4" s="34" t="inlineStr">
         <is>
           <t>6척 해당</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>3K / Korea</t>
         </is>
       </c>
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>Rudder shaft &amp; pump</t>
         </is>
       </c>
-      <c r="C5" s="34" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>Klüberbio LG 39-701 N</t>
         </is>
       </c>
-      <c r="D5" s="34" t="inlineStr">
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>승인현황 p.6</t>
         </is>
       </c>
-      <c r="F5" s="36" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>●</t>
         </is>
@@ -5071,32 +5075,32 @@
       <c r="F6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>Kawasaki Heavy Industries / Japan</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Thruster 기어유</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>Klüberbio EG 2-100</t>
         </is>
       </c>
-      <c r="D7" s="34" t="inlineStr">
+      <c r="D7" s="35" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="E7" s="35" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>승인현황 p.3 · 2018-08 업데이트 p.6</t>
         </is>
       </c>
-      <c r="F7" s="36" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>●</t>
         </is>
@@ -5131,32 +5135,32 @@
       <c r="F8" s="6" t="inlineStr"/>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>Hyundai Heavy Industries / Korea</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>Thruster 기어유</t>
         </is>
       </c>
-      <c r="C9" s="34" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>Klüberbio EG 2-100</t>
         </is>
       </c>
-      <c r="D9" s="34" t="inlineStr">
+      <c r="D9" s="35" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="E9" s="35" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>승인현황 p.3 · 2018-08 업데이트 p.6</t>
         </is>
       </c>
-      <c r="F9" s="36" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>●</t>
         </is>
@@ -5219,354 +5223,354 @@
       <c r="F11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>WÄRTSILÄ Japan (former JMT)</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>Stern tube 씰</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>Klüberbio RM 2-100 / RM 2-150</t>
         </is>
       </c>
-      <c r="D12" s="34" t="inlineStr">
+      <c r="D12" s="35" t="inlineStr">
         <is>
           <t>BIO FKM seal rings 승인</t>
         </is>
       </c>
-      <c r="E12" s="35" t="inlineStr">
+      <c r="E12" s="36" t="inlineStr">
         <is>
           <t>승인현황 p.1</t>
         </is>
       </c>
-      <c r="F12" s="36" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>WÄRTSILÄ Sweden AB (Cedervall)</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>Stern tube 씰</t>
         </is>
       </c>
-      <c r="C13" s="34" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>Klüberbio RM 2-100 / RM 2-150</t>
         </is>
       </c>
-      <c r="D13" s="34" t="inlineStr">
+      <c r="D13" s="35" t="inlineStr">
         <is>
           <t>RM 2-150 승인 · RM 2-100 은 신형 face seal 용</t>
         </is>
       </c>
-      <c r="E13" s="35" t="inlineStr">
+      <c r="E13" s="36" t="inlineStr">
         <is>
           <t>승인현황 p.1</t>
         </is>
       </c>
-      <c r="F13" s="36" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>WÄRTSILÄ UK (Deep Sea Seals)</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Stern tube 씰</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>Klüberbio RM 2-100 / RM 2-150</t>
         </is>
       </c>
-      <c r="D14" s="34" t="inlineStr">
+      <c r="D14" s="35" t="inlineStr">
         <is>
           <t>여러 씰 타입 승인 (최신 목록 별도 확인)</t>
         </is>
       </c>
-      <c r="E14" s="35" t="inlineStr">
+      <c r="E14" s="36" t="inlineStr">
         <is>
           <t>승인현황 p.1</t>
         </is>
       </c>
-      <c r="F14" s="36" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>WÄRTSILÄ Japan</t>
         </is>
       </c>
-      <c r="B15" s="34" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>Rudder shaft 씰</t>
         </is>
       </c>
-      <c r="C15" s="34" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>Klüberbio AG 39-602</t>
         </is>
       </c>
-      <c r="D15" s="34" t="inlineStr">
+      <c r="D15" s="35" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="E15" s="35" t="inlineStr">
+      <c r="E15" s="36" t="inlineStr">
         <is>
           <t>승인현황 p.6</t>
         </is>
       </c>
-      <c r="F15" s="36" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>WÄRTSILÄ Propulsion / Holland</t>
         </is>
       </c>
-      <c r="B16" s="34" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Thruster 기어유</t>
         </is>
       </c>
-      <c r="C16" s="34" t="inlineStr">
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t>Klüberbio EG 2-150</t>
         </is>
       </c>
-      <c r="D16" s="34" t="inlineStr">
+      <c r="D16" s="35" t="inlineStr">
         <is>
           <t>승인 (사전 협의 필요)</t>
         </is>
       </c>
-      <c r="E16" s="35" t="inlineStr">
+      <c r="E16" s="36" t="inlineStr">
         <is>
           <t>승인현황 p.4 · 업데이트 p.9</t>
         </is>
       </c>
-      <c r="F16" s="36" t="inlineStr">
+      <c r="F16" s="37" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>KEMEL / Japan</t>
         </is>
       </c>
-      <c r="B17" s="34" t="inlineStr">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>Stern tube 씰</t>
         </is>
       </c>
-      <c r="C17" s="34" t="inlineStr">
+      <c r="C17" s="35" t="inlineStr">
         <is>
           <t>Klüberbio RM 2-100 / RM 2-150</t>
         </is>
       </c>
-      <c r="D17" s="34" t="inlineStr">
+      <c r="D17" s="35" t="inlineStr">
         <is>
           <t>승인 — 단, 선박별 개별 승인 필요</t>
         </is>
       </c>
-      <c r="E17" s="35" t="inlineStr">
+      <c r="E17" s="36" t="inlineStr">
         <is>
           <t>승인현황 p.1</t>
         </is>
       </c>
-      <c r="F17" s="36" t="inlineStr">
+      <c r="F17" s="37" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>KEMEL / Japan</t>
         </is>
       </c>
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>Thruster 씰</t>
         </is>
       </c>
-      <c r="C18" s="34" t="inlineStr">
+      <c r="C18" s="35" t="inlineStr">
         <is>
           <t>Klüberbio EG 2-100 / EG 2-150</t>
         </is>
       </c>
-      <c r="D18" s="34" t="inlineStr">
+      <c r="D18" s="35" t="inlineStr">
         <is>
           <t>신형 BIO seal ring 승인</t>
         </is>
       </c>
-      <c r="E18" s="35" t="inlineStr">
+      <c r="E18" s="36" t="inlineStr">
         <is>
           <t>승인현황 p.2</t>
         </is>
       </c>
-      <c r="F18" s="36" t="inlineStr">
+      <c r="F18" s="37" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>SKF Marine (Simplex, 구 Blohm+Voss)</t>
         </is>
       </c>
-      <c r="B19" s="34" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>Stern tube 씰</t>
         </is>
       </c>
-      <c r="C19" s="34" t="inlineStr">
+      <c r="C19" s="35" t="inlineStr">
         <is>
           <t>Klüberbio RM 2-100 / RM 2-150</t>
         </is>
       </c>
-      <c r="D19" s="34" t="inlineStr">
+      <c r="D19" s="35" t="inlineStr">
         <is>
           <t>FKM (Viton Pod · Viton Bio) 씰링 재질 승인</t>
         </is>
       </c>
-      <c r="E19" s="35" t="inlineStr">
+      <c r="E19" s="36" t="inlineStr">
         <is>
           <t>승인현황 p.1</t>
         </is>
       </c>
-      <c r="F19" s="36" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="34" t="inlineStr">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>SKF Marine (Simplex)</t>
         </is>
       </c>
-      <c r="B20" s="34" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>Thruster 씰</t>
         </is>
       </c>
-      <c r="C20" s="34" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>Klüberbio EG 2-68 / 100 / 150</t>
         </is>
       </c>
-      <c r="D20" s="34" t="inlineStr">
+      <c r="D20" s="35" t="inlineStr">
         <is>
           <t>FKM (Viton Pod · Viton BIO) 승인</t>
         </is>
       </c>
-      <c r="E20" s="35" t="inlineStr">
+      <c r="E20" s="36" t="inlineStr">
         <is>
           <t>승인현황 p.2 · 업데이트 p.12~14</t>
         </is>
       </c>
-      <c r="F20" s="36" t="inlineStr">
+      <c r="F20" s="37" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="34" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>MAN Diesel &amp; Turbo SE / Denmark</t>
         </is>
       </c>
-      <c r="B21" s="34" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>Propeller cap</t>
         </is>
       </c>
-      <c r="C21" s="34" t="inlineStr">
+      <c r="C21" s="35" t="inlineStr">
         <is>
           <t>Klüberbio BM 32-142 / AG 39-602 /
 LG 39-701 N</t>
         </is>
       </c>
-      <c r="D21" s="34" t="inlineStr">
+      <c r="D21" s="35" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="E21" s="35" t="inlineStr">
+      <c r="E21" s="36" t="inlineStr">
         <is>
           <t>승인현황 p.6</t>
         </is>
       </c>
-      <c r="F21" s="36" t="inlineStr">
+      <c r="F21" s="37" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="34" t="inlineStr">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>Mecklenburger Metallguss / Germany</t>
         </is>
       </c>
-      <c r="B22" s="34" t="inlineStr">
+      <c r="B22" s="35" t="inlineStr">
         <is>
           <t>Propeller cap</t>
         </is>
       </c>
-      <c r="C22" s="34" t="inlineStr">
+      <c r="C22" s="35" t="inlineStr">
         <is>
           <t>Klüberbio BM 32-142 / AG 39-602 /
 LG 39-701 N</t>
         </is>
       </c>
-      <c r="D22" s="34" t="inlineStr">
+      <c r="D22" s="35" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="E22" s="35" t="inlineStr">
+      <c r="E22" s="36" t="inlineStr">
         <is>
           <t>승인현황 p.6</t>
         </is>
       </c>
-      <c r="F22" s="36" t="inlineStr">
+      <c r="F22" s="37" t="inlineStr">
         <is>
           <t>●</t>
         </is>
@@ -5657,103 +5661,103 @@
       <c r="F25" s="6" t="inlineStr"/>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="32" t="inlineStr">
+      <c r="A28" s="33" t="inlineStr">
         <is>
           <t>[2] SKF Marine EAL 리스트 — 6척 관련 브랜드 및 Klüber 대응 후보 발췌</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="33" t="inlineStr">
+      <c r="A29" s="34" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="B29" s="33" t="inlineStr">
+      <c r="B29" s="34" t="inlineStr">
         <is>
           <t>제품명</t>
         </is>
       </c>
-      <c r="C29" s="33" t="inlineStr">
+      <c r="C29" s="34" t="inlineStr">
         <is>
           <t>점도 (cSt @40℃)</t>
         </is>
       </c>
-      <c r="D29" s="33" t="inlineStr">
+      <c r="D29" s="34" t="inlineStr">
         <is>
           <t>분류</t>
         </is>
       </c>
-      <c r="E29" s="33" t="inlineStr">
+      <c r="E29" s="34" t="inlineStr">
         <is>
           <t>씰링 재질</t>
         </is>
       </c>
-      <c r="F29" s="33" t="inlineStr">
+      <c r="F29" s="34" t="inlineStr">
         <is>
           <t>6척 사용 여부</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="35" t="inlineStr">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>Total Lubmarine</t>
         </is>
       </c>
-      <c r="B30" s="34" t="inlineStr">
+      <c r="B30" s="35" t="inlineStr">
         <is>
           <t>Bioneptan 150</t>
         </is>
       </c>
-      <c r="C30" s="35" t="inlineStr">
+      <c r="C30" s="36" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D30" s="35" t="inlineStr">
+      <c r="D30" s="36" t="inlineStr">
         <is>
           <t>Sterntube Oil</t>
         </is>
       </c>
-      <c r="E30" s="35" t="inlineStr">
+      <c r="E30" s="36" t="inlineStr">
         <is>
           <t>FKM Pod, FKM Bio</t>
         </is>
       </c>
-      <c r="F30" s="37" t="inlineStr">
+      <c r="F30" s="38" t="inlineStr">
         <is>
           <t>SK AUDACE 사용 중</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="35" t="inlineStr">
+      <c r="A31" s="36" t="inlineStr">
         <is>
           <t>Total Lubmarine</t>
         </is>
       </c>
-      <c r="B31" s="34" t="inlineStr">
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>Bioneptan HT 100</t>
         </is>
       </c>
-      <c r="C31" s="35" t="inlineStr">
+      <c r="C31" s="36" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D31" s="35" t="inlineStr">
+      <c r="D31" s="36" t="inlineStr">
         <is>
           <t>Multipurpose Oil</t>
         </is>
       </c>
-      <c r="E31" s="35" t="inlineStr">
+      <c r="E31" s="36" t="inlineStr">
         <is>
           <t>FKM Pod, FKM Bio</t>
         </is>
       </c>
-      <c r="F31" s="37" t="inlineStr">
+      <c r="F31" s="38" t="inlineStr">
         <is>
           <t>PRISM AGILITY · SK AUDACE 사용 중</t>
         </is>
@@ -5856,32 +5860,32 @@
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="35" t="inlineStr">
+      <c r="A35" s="36" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="B35" s="34" t="inlineStr">
+      <c r="B35" s="35" t="inlineStr">
         <is>
           <t>Mobil SHC Aware Gear 100</t>
         </is>
       </c>
-      <c r="C35" s="35" t="inlineStr">
+      <c r="C35" s="36" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D35" s="35" t="inlineStr">
+      <c r="D35" s="36" t="inlineStr">
         <is>
           <t>Gear Oil</t>
         </is>
       </c>
-      <c r="E35" s="35" t="inlineStr">
+      <c r="E35" s="36" t="inlineStr">
         <is>
           <t>FKM Pod, FKM Bio</t>
         </is>
       </c>
-      <c r="F35" s="37" t="inlineStr">
+      <c r="F35" s="38" t="inlineStr">
         <is>
           <t>PRISM AGILITY 사용 중</t>
         </is>
@@ -6137,7 +6141,7 @@
           <t>FKM Pod, FKM Bio</t>
         </is>
       </c>
-      <c r="F43" s="38" t="inlineStr">
+      <c r="F43" s="39" t="inlineStr">
         <is>
           <t>대응 후보</t>
         </is>
@@ -6169,7 +6173,7 @@
           <t>FKM Pod, FKM Bio</t>
         </is>
       </c>
-      <c r="F44" s="38" t="inlineStr">
+      <c r="F44" s="39" t="inlineStr">
         <is>
           <t>대응 후보</t>
         </is>
@@ -6233,7 +6237,7 @@
           <t>FKM Pod, FKM Bio</t>
         </is>
       </c>
-      <c r="F46" s="38" t="inlineStr">
+      <c r="F46" s="39" t="inlineStr">
         <is>
           <t>대응 후보</t>
         </is>
@@ -6272,7 +6276,7 @@
       </c>
     </row>
     <row r="49" ht="130" customHeight="1">
-      <c r="A49" s="20" t="inlineStr">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>▣ 출처 및 단서
   · Klüber EAL Approval Status, 2018-02-13 (GATE-MOG / Dirk Fabry, 6p)
